--- a/BMW_SecOc.xlsx
+++ b/BMW_SecOc.xlsx
@@ -1,35 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_XuhuaRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF77DBD-810F-4424-9630-76E52256938D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AE3AB0-2D55-4CAF-B40E-491A28387350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="551" firstSheet="1" activeTab="4" xr2:uid="{EE3554E5-5B85-4F6F-95D2-24E55C4E92D2}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="551" firstSheet="4" activeTab="8" xr2:uid="{EE3554E5-5B85-4F6F-95D2-24E55C4E92D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="2" r:id="rId1"/>
     <sheet name="Code_Flow" sheetId="8" r:id="rId2"/>
-    <sheet name="Structure" sheetId="131" r:id="rId3"/>
-    <sheet name="PDU" sheetId="6" r:id="rId4"/>
-    <sheet name="PDU_Flow" sheetId="7" r:id="rId5"/>
-    <sheet name="Key-ID" sheetId="12" r:id="rId6"/>
-    <sheet name="TxManipulation" sheetId="11" r:id="rId7"/>
-    <sheet name="Csm" sheetId="132" r:id="rId8"/>
-    <sheet name="CntMsgRx" sheetId="19" r:id="rId9"/>
-    <sheet name="CollectPduPropertiesList" sheetId="13" r:id="rId10"/>
-    <sheet name="SFun_SecOCMainSetup" sheetId="9" r:id="rId11"/>
-    <sheet name="SFun_CounterManagerInterface" sheetId="14" r:id="rId12"/>
-    <sheet name="SFun_CounterRequestMessage" sheetId="15" r:id="rId13"/>
-    <sheet name="DoCyclicClientStateMachineOpera" sheetId="133" r:id="rId14"/>
-    <sheet name="SFun_DoCyclicMasterStateMachine" sheetId="17" r:id="rId15"/>
-    <sheet name="SFun_DoCyclicClientStateMachine" sheetId="16" r:id="rId16"/>
-    <sheet name="UC" sheetId="134" r:id="rId17"/>
+    <sheet name="UserCode_FeatureData" sheetId="131" r:id="rId3"/>
+    <sheet name="Ds_PduFeatureHandle" sheetId="135" r:id="rId4"/>
+    <sheet name="Pointer" sheetId="136" r:id="rId5"/>
+    <sheet name="PDU" sheetId="6" r:id="rId6"/>
+    <sheet name="PDU_Flow" sheetId="7" r:id="rId7"/>
+    <sheet name="Key-ID" sheetId="12" r:id="rId8"/>
+    <sheet name="TxManipulation" sheetId="11" r:id="rId9"/>
+    <sheet name="CntMsgRx" sheetId="19" r:id="rId10"/>
+    <sheet name="Csm" sheetId="132" r:id="rId11"/>
+    <sheet name="CollectPduPropertiesList" sheetId="13" r:id="rId12"/>
+    <sheet name="SFun_SecOCMainSetup" sheetId="9" r:id="rId13"/>
+    <sheet name="SFun_CounterManagerInterface" sheetId="14" r:id="rId14"/>
+    <sheet name="SFun_CounterRequestMessage" sheetId="15" r:id="rId15"/>
+    <sheet name="DoCyclicClientStateMachineOpera" sheetId="133" r:id="rId16"/>
+    <sheet name="SFun_DoCyclicMasterStateMachine" sheetId="17" r:id="rId17"/>
+    <sheet name="SFun_DoCyclicClientStateMachine" sheetId="16" r:id="rId18"/>
+    <sheet name="UC" sheetId="134" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="561">
   <si>
     <t>DsBusCustomCode_onPduFeatureExecutionPrivate(pduFeatureHandle)</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -15350,161 +15352,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PduFeatureHandle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t>PduPropertiesContainer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> *pduProps
-rtlib_malloc(sizeof(PduPropertiesContainer))</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>DsBusCustomCodePduFeatureInfoType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">DsBusCustomCodeHandleParameterStruct </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>Handle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-DsBusCustomCodePduFeatureParameterStruct</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> PduFeature</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t>HandleDsBusCustomCodeFeatureParameterStruct</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> Feature</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t>UserCode_FeatureData</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> *</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>pduFeatData</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-rtlib_malloc(sizeof(UserCode_FeatureData))</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">uint32 Feature
-uint32 FeatureIsSet
-uint8* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>FeatureDataPtr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-uint32 FeatureDataPtrIsSet</t>
-    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -17478,191 +17326,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>METHOD#1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">:
-{
-userDefinedAuthenticator = 0,
-automaticAuthenticatorCalc = 1
-} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">AuthenticatorCalculationMode
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">*authenticatorPtr = Crypto_Job-&gt;PrimitiveInputOutput-&gt;outputPtr;
-*authenticatorLengthInBytes = Crypto_Job-&gt;jobPrimitiveInfo-&gt;primitiveInfo-&gt;resultLength
-resultLength = sizeof(dataId) + dataLength + freshnessValueLength / 8
-______________________________________________________________________________________________
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>METHOD#2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">:
-*authenticatorPtr = PtrSecOCTxPduFeature.UserDefinedAuthenticatorPtr
-*authenticatorLengthInBytes = (MacTruncatedLength + 7) / 8
-______________________________________________________________________________________________
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>METHOD#3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SFun先执行，接收BusManger的Manipulation值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiBold"/>
-        <family val="3"/>
-      </rPr>
-      <t>SecOCTxRxPduManipulationSFunc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>:FindPduFeatureItem_:
-for (int i = 0; i &lt; MAX_NUM_MAC_DATA_BYTES; i++) {
-pduProps-&gt;AuthenticatorBytesOverwriteEnable[i]  = (boolean*)authenticatorOverwriteEnablePtr[i]
-pduProps-&gt;AuthenticatorBytesOverwriteValue[i]   = (uint8*)authenticatorOverwriteValuePtr[i]}
-UserCode_Csm_GetAuthenticatorPtr(pduFeatData, &amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>readDataPtr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>, &amp;dataLengthInBytes)
-WriteDataArray(</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t>readDataPtr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Mono SemiLight"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, macValuePtr, dataLengthInBytes, MAX_NUM_MAC_DATA_BYTES)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>此处MAC直接从PDU获取，非Manipulation值</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SOME/IP</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -20194,29 +19857,397 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ClientCntValue.c</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GetClientCounterValue
-IsReceivedCounterValueOutsideAcceptWindow</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">                                                </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Code SemiBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>HandleDsBusCustomCodeFeatureParameterStruct</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Feature</t>
+    </r>
+  </si>
+  <si>
+    <t>DsBusCustomCodeHandleParameterStruct Handle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>DsBusCustomCodePduFeatureParameterStruct</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PduFeature</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>DsBusCustomCodePduHandle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Pdu
+DsBusCustomCodeEcuHandle Ecu
+DsBusCustomCodeCommunicationClusterHandle CommunicationCluster</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">uint32 Feature
+uint32 FeatureIsSet
+uint8* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>FeatureDataPtr ( --&gt; UserCode_FeatureData, PduFeatData / (uint8*) PduFeatureDataPtr)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+uint32 FeatureDataPtrIsSet</t>
+    </r>
+  </si>
+  <si>
+    <t>UserCode_FeatureData</t>
+  </si>
+  <si>
+    <t>uint8* PduPropertiesContainer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono SemiBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>DsBusCustomCodePduFeatureHandle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+PduFeatureHandle</t>
+    </r>
+  </si>
+  <si>
+    <t>{UserCode_FeatureData}</t>
+  </si>
+  <si>
+    <t>*PduPropertiesContainer</t>
+  </si>
+  <si>
+    <t>(*PduProps)</t>
+  </si>
+  <si>
+    <t>{PduPropertiesContainer}</t>
+  </si>
+  <si>
+    <t>{DsBusCustomFeatureInfoType}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono Light"/>
+        <family val="3"/>
+      </rPr>
+      <t>uint8* PduFeaturehandle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono Light"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono Light"/>
+        <family val="3"/>
+      </rPr>
+      <t>DsBusCustomPduFeatureHandle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono Light"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>uint8* Feature.FeatureDataPtr</t>
+  </si>
+  <si>
+    <t>*PduFeatData
+uint8* PduFeatureDataPtr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>METHOD#1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">:
+{
+userDefinedAuthenticator = 0,
+automaticAuthenticatorCalc = 1
+} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">AuthenticatorCalculationMode
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">*authenticatorPtr = Crypto_Job-&gt;PrimitiveInputOutput-&gt;outputPtr;
+*authenticatorLengthInBytes = Crypto_Job-&gt;jobPrimitiveInfo-&gt;primitiveInfo-&gt;resultLength
+resultLength = sizeof(dataId) + dataLength + freshnessValueLength / 8
+______________________________________________________________________________________________
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>METHOD#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">:
+*authenticatorPtr = PtrSecOCTxPduFeature.UserDefinedAuthenticatorPtr
+*authenticatorLengthInBytes = (MacTruncatedLength + 7) / 8
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
         <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>DataToAuthenticator</t>
+      <t>在 C 语言整数除法中，(a + 7) / 8 是实现 向上取整（ceil） 的标准写法，用于确保即使 MAC 长度不是整字节（例如 64 位正好 8 字节，或 96 位需要 12 字节），也能分配足够的空间来容纳所有有效位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+______________________________________________________________________________________________
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>METHOD#3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SFun先执行，接收BusManger的Manipulation值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>SecOCTxRxPduManipulationSFunc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>:FindPduFeatureItem_:
+for (int i = 0; i &lt; MAX_NUM_MAC_DATA_BYTES; i++) {
+pduProps-&gt;AuthenticatorBytesOverwriteEnable[i]  = (boolean*)authenticatorOverwriteEnablePtr[i]
+pduProps-&gt;AuthenticatorBytesOverwriteValue[i]   = (uint8*)authenticatorOverwriteValuePtr[i]}
+UserCode_Csm_GetAuthenticatorPtr(pduFeatData, &amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>readDataPtr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>, &amp;dataLengthInBytes)
+WriteDataArray(</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t>readDataPtr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cascadia Mono SemiLight"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, macValuePtr, dataLengthInBytes, MAX_NUM_MAC_DATA_BYTES)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此处MAC直接从PDU获取，非Manipulation值</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -20225,7 +20256,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="132" x14ac:knownFonts="1">
+  <fonts count="137" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -21099,16 +21130,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cascadia Mono Light"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono Light"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono Light"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Cascadia Mono Light"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="4"/>
+      <color theme="9" tint="-0.499984740745262"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -21301,8 +21361,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="125">
+  <borders count="131">
     <border>
       <left/>
       <right/>
@@ -22428,19 +22494,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color auto="1"/>
       </left>
@@ -22462,64 +22515,12 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="hair">
         <color auto="1"/>
       </top>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -22964,6 +22965,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -22971,7 +23115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="568">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -23134,6 +23278,9 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -23653,61 +23800,28 @@
     <xf numFmtId="0" fontId="24" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -23737,13 +23851,13 @@
     <xf numFmtId="0" fontId="5" fillId="26" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -23755,64 +23869,64 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="94" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="100" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="101" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="96" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="102" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="97" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="100" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="102" fillId="29" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="29" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="29" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="29" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="102" fillId="29" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="29" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="103" fillId="29" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="29" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="4" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="29" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="29" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="29" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="4" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="4" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="4" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23821,28 +23935,28 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="4" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="4" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -24085,6 +24199,72 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -24169,52 +24349,52 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -24334,17 +24514,14 @@
     <xf numFmtId="0" fontId="40" fillId="14" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="8" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="8" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="8" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="8" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="4" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -24493,16 +24670,16 @@
     <xf numFmtId="0" fontId="108" fillId="22" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="31" borderId="121" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="31" borderId="116" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="31" borderId="122" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="31" borderId="117" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="31" borderId="123" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="31" borderId="118" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="31" borderId="124" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="31" borderId="119" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="31" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -24570,12 +24747,6 @@
     </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24586,10 +24757,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFF5050"/>
+      <color rgb="FFFF00FF"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFFDDFF"/>
-      <color rgb="FFFF00FF"/>
+      <color rgb="FFFF5050"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FFF4F9F1"/>
       <color rgb="FFFFCCCC"/>
@@ -24613,23 +24784,82 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2609021</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>298174</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3740150</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2617304</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3740150</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="直接箭头连接符 2">
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52024DC7-429A-92B7-2438-A7FA81F910CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14891CCD-519E-5666-423D-0B1EDF0FDB54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4349750" y="1358900"/>
+          <a:ext cx="0" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3524250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9181F3BA-194A-851C-5600-7D27A0AF2498}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24637,13 +24867,64 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="5855804" y="1739348"/>
-          <a:ext cx="8283" cy="1681369"/>
+          <a:off x="9067800" y="1114425"/>
+          <a:ext cx="647700" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A80EF842-C169-4A79-EDC6-F49FBB1F780E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9078058" y="929542"/>
+          <a:ext cx="630115" cy="184150"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln w="12700">
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -24667,196 +24948,113 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2642152</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>33131</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>4547152</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>99392</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7327</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="矩形 7">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C1A2AF7-834D-934A-DFE6-2467F2BC6DDC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{666CEB88-2559-C7F3-6FB9-9FD9038EF414}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5888935" y="1474305"/>
-          <a:ext cx="1905000" cy="381000"/>
+        <a:xfrm flipV="1">
+          <a:off x="4850423" y="1875692"/>
+          <a:ext cx="703385" cy="490904"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FF00FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
         </a:lnRef>
-        <a:fillRef idx="1">
+        <a:fillRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:fillRef>
         <a:effectRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2675283</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>33130</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3702326</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>2601057</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>179021</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="矩形 8">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07264049-6CEE-DACF-B5B0-E9589A53829C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEB507E-0AC8-0985-F7D8-F9E9092A5E9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10485783" y="1474304"/>
-          <a:ext cx="1027043" cy="472109"/>
+        <a:xfrm flipH="1">
+          <a:off x="4850423" y="849923"/>
+          <a:ext cx="3297115" cy="61790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
         </a:lnRef>
-        <a:fillRef idx="1">
+        <a:fillRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:fillRef>
         <a:effectRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>41413</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1209261</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>298174</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="矩形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48809522-3959-C2FE-D988-7CBF9B682B64}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11570804" y="389283"/>
-          <a:ext cx="1167848" cy="1350065"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -28287,7 +28485,7 @@
       <c r="B2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="403" t="s">
+      <c r="C2" s="415" t="s">
         <v>88</v>
       </c>
     </row>
@@ -28298,7 +28496,7 @@
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="404"/>
+      <c r="C3" s="416"/>
     </row>
     <row r="4" spans="1:3" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -28307,7 +28505,7 @@
       <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="405"/>
+      <c r="C4" s="417"/>
     </row>
     <row r="5" spans="1:3" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -28340,67 +28538,67 @@
       <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:3" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="411" t="s">
+      <c r="A9" s="423" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="411"/>
-      <c r="C9" s="412"/>
+      <c r="B9" s="423"/>
+      <c r="C9" s="424"/>
     </row>
     <row r="10" spans="1:3" ht="287.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="406" t="s">
+      <c r="C10" s="418" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="407"/>
+      <c r="C11" s="419"/>
     </row>
     <row r="12" spans="1:3" ht="257.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="409" t="s">
+      <c r="A12" s="421" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="92" t="s">
+      <c r="B12" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="407"/>
+      <c r="C12" s="419"/>
     </row>
     <row r="13" spans="1:3" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="410"/>
-      <c r="B13" s="92" t="s">
+      <c r="A13" s="422"/>
+      <c r="B13" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="408"/>
+      <c r="C13" s="420"/>
     </row>
     <row r="14" spans="1:3" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="95" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="406" t="s">
+      <c r="C14" s="418" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="92" t="s">
+      <c r="B15" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="408"/>
+      <c r="C15" s="420"/>
     </row>
     <row r="16" spans="1:3" ht="378.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
@@ -28409,7 +28607,7 @@
       <c r="B16" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="403"/>
+      <c r="C16" s="415"/>
     </row>
     <row r="17" spans="1:3" ht="110.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
@@ -28418,7 +28616,7 @@
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="404"/>
+      <c r="C17" s="416"/>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
@@ -28445,16 +28643,16 @@
       <c r="B20" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="400" t="s">
+      <c r="C20" s="412" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="122" t="s">
+      <c r="A21" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="123"/>
-      <c r="C21" s="401"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="413"/>
     </row>
     <row r="22" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
@@ -28463,7 +28661,7 @@
       <c r="B22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="401"/>
+      <c r="C22" s="413"/>
     </row>
     <row r="23" spans="1:3" ht="370.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
@@ -28472,14 +28670,14 @@
       <c r="B23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="402"/>
+      <c r="C23" s="414"/>
     </row>
     <row r="24" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="399" t="s">
+      <c r="C24" s="411" t="s">
         <v>53</v>
       </c>
     </row>
@@ -28488,7 +28686,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="399"/>
+      <c r="C25" s="411"/>
     </row>
     <row r="26" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
@@ -28497,7 +28695,7 @@
       <c r="B26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="399"/>
+      <c r="C26" s="411"/>
     </row>
     <row r="27" spans="1:3" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
@@ -28506,35 +28704,35 @@
       <c r="B27" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="399"/>
+      <c r="C27" s="411"/>
     </row>
     <row r="28" spans="1:3" ht="110.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="12"/>
-      <c r="C28" s="399"/>
+      <c r="C28" s="411"/>
     </row>
     <row r="29" spans="1:3" ht="224.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="12"/>
-      <c r="C29" s="399"/>
+      <c r="C29" s="411"/>
     </row>
     <row r="30" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="124" t="s">
+      <c r="A30" s="125" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="399"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="411"/>
     </row>
     <row r="31" spans="1:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>77</v>
       </c>
       <c r="B31" s="12"/>
-      <c r="C31" s="396"/>
+      <c r="C31" s="408"/>
     </row>
     <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="40" t="s">
@@ -28550,7 +28748,7 @@
       <c r="B33" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="395" t="s">
+      <c r="C33" s="407" t="s">
         <v>54</v>
       </c>
     </row>
@@ -28561,32 +28759,32 @@
       <c r="B34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="396"/>
+      <c r="C34" s="408"/>
     </row>
     <row r="35" spans="1:3" ht="401.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="397" t="s">
+      <c r="A35" s="409" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="46" t="s">
         <v>345</v>
       </c>
-      <c r="C35" s="395" t="s">
+      <c r="C35" s="407" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="215.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="398"/>
+      <c r="A36" s="410"/>
       <c r="B36" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="399"/>
+      <c r="C36" s="411"/>
     </row>
     <row r="37" spans="1:3" ht="297.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="398"/>
+      <c r="A37" s="410"/>
       <c r="B37" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="399"/>
+      <c r="C37" s="411"/>
     </row>
     <row r="38" spans="1:3" ht="135.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
@@ -28595,7 +28793,7 @@
       <c r="B38" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="396"/>
+      <c r="C38" s="408"/>
     </row>
     <row r="39" spans="1:3" ht="393.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
@@ -28604,7 +28802,7 @@
       <c r="B39" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C39" s="121" t="s">
+      <c r="C39" s="122" t="s">
         <v>53</v>
       </c>
     </row>
@@ -28612,10 +28810,10 @@
       <c r="A40" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B40" s="247" t="s">
+      <c r="B40" s="248" t="s">
         <v>346</v>
       </c>
-      <c r="C40" s="121" t="s">
+      <c r="C40" s="122" t="s">
         <v>347</v>
       </c>
     </row>
@@ -28640,217 +28838,496 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03CDB98-0589-4698-B3D8-29BB64912381}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="73.625" style="178" customWidth="1"/>
+    <col min="2" max="2" width="182.625" style="178" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="178"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="271" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B2" s="178" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="406" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="178" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="406"/>
+      <c r="B4" s="178" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="178" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="178" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="178" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="270"/>
+      <c r="B7" s="270"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="271" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="178" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9" s="178" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="178" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="406" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" s="178" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="406"/>
+      <c r="B12" s="178" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="178" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="178" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="178" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="178" t="s">
+        <v>356</v>
+      </c>
+      <c r="B15" s="178" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="272" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="273" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="273" t="s">
+        <v>398</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5038E81-DFEA-4A7B-94DE-1888A725E6E8}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="106.875" style="47" customWidth="1"/>
+    <col min="2" max="2" width="128.625" style="47" customWidth="1"/>
+    <col min="3" max="3" width="69" style="47" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="286" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="284"/>
+      <c r="C1" s="285"/>
+    </row>
+    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="290" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="291"/>
+      <c r="C2" s="299"/>
+    </row>
+    <row r="3" spans="1:3" ht="202.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="292" t="s">
+        <v>414</v>
+      </c>
+      <c r="B3" s="293" t="s">
+        <v>428</v>
+      </c>
+      <c r="C3" s="300" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="289" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="287"/>
+      <c r="C4" s="288"/>
+    </row>
+    <row r="5" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="490" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="294" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="299" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="491"/>
+      <c r="B6" s="295" t="s">
+        <v>434</v>
+      </c>
+      <c r="C6" s="301" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="492" t="s">
+        <v>416</v>
+      </c>
+      <c r="B7" s="296" t="s">
+        <v>427</v>
+      </c>
+      <c r="C7" s="304" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="288" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="492"/>
+      <c r="B8" s="295" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="301" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="492"/>
+      <c r="B9" s="295" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="302"/>
+    </row>
+    <row r="10" spans="1:3" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="492" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="295" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="301" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="492"/>
+      <c r="B11" s="295" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="302" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="492"/>
+      <c r="B12" s="295" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="301" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="297" t="s">
+        <v>425</v>
+      </c>
+      <c r="B13" s="298"/>
+      <c r="C13" s="303" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" s="283"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37DE18C-5A4D-4B20-AE81-AC21649CDBCC}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.625" style="151" customWidth="1"/>
-    <col min="2" max="2" width="49.875" style="151" customWidth="1"/>
-    <col min="3" max="3" width="114.625" style="151" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="151"/>
+    <col min="1" max="1" width="40.625" style="152" customWidth="1"/>
+    <col min="2" max="2" width="49.875" style="152" customWidth="1"/>
+    <col min="3" max="3" width="114.625" style="152" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="152"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="154" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="155" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="175" t="s">
+      <c r="C1" s="176" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="152" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+    <row r="2" spans="1:3" s="153" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="156" t="s">
         <v>224</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="164"/>
-    </row>
-    <row r="3" spans="1:3" s="152" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="155" t="s">
+      <c r="B2" s="171"/>
+      <c r="C2" s="165"/>
+    </row>
+    <row r="3" spans="1:3" s="153" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="156" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="164"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="165"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="157" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="171"/>
-      <c r="C4" s="165"/>
+      <c r="B4" s="172"/>
+      <c r="C4" s="166"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="156" t="s">
+      <c r="A5" s="157" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="171"/>
-      <c r="C5" s="165"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="166"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="157" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="165"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="166"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="156" t="s">
+      <c r="A7" s="157" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="171"/>
-      <c r="C7" s="165"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="166"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="157" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="171"/>
-      <c r="C8" s="165" t="s">
+      <c r="B8" s="172"/>
+      <c r="C8" s="166" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="156" t="s">
+      <c r="A9" s="157" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="171"/>
-      <c r="C9" s="165"/>
+      <c r="B9" s="172"/>
+      <c r="C9" s="166"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="156" t="s">
+      <c r="A10" s="157" t="s">
         <v>221</v>
       </c>
-      <c r="B10" s="171" t="s">
+      <c r="B10" s="172" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="165"/>
+      <c r="C10" s="166"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="162" t="s">
+      <c r="A11" s="163" t="s">
         <v>219</v>
       </c>
-      <c r="B11" s="171"/>
-      <c r="C11" s="165"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="166"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="156" t="s">
+      <c r="A12" s="157" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="171"/>
-      <c r="C12" s="165"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="166"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="156" t="s">
+      <c r="A13" s="157" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="165"/>
+      <c r="B13" s="172"/>
+      <c r="C13" s="166"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="157" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="171"/>
-      <c r="C14" s="165"/>
+      <c r="B14" s="172"/>
+      <c r="C14" s="166"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="162" t="s">
         <v>215</v>
       </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="165"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="166"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="160" t="s">
+      <c r="A16" s="161" t="s">
         <v>214</v>
       </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="165"/>
+      <c r="B16" s="172"/>
+      <c r="C16" s="166"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="156" t="s">
+      <c r="A17" s="157" t="s">
         <v>213</v>
       </c>
-      <c r="B17" s="171"/>
-      <c r="C17" s="165"/>
+      <c r="B17" s="172"/>
+      <c r="C17" s="166"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="157"/>
-      <c r="B18" s="170" t="s">
+      <c r="A18" s="158"/>
+      <c r="B18" s="171" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="165"/>
+      <c r="C18" s="166"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="157"/>
-      <c r="B19" s="174" t="s">
+      <c r="A19" s="158"/>
+      <c r="B19" s="175" t="s">
         <v>211</v>
       </c>
-      <c r="C19" s="165"/>
+      <c r="C19" s="166"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="157"/>
-      <c r="B20" s="171" t="s">
+      <c r="A20" s="158"/>
+      <c r="B20" s="172" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="165"/>
+      <c r="C20" s="166"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="157"/>
-      <c r="B21" s="172"/>
-      <c r="C21" s="166" t="s">
+      <c r="A21" s="158"/>
+      <c r="B21" s="173"/>
+      <c r="C21" s="167" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="157"/>
-      <c r="B22" s="172"/>
-      <c r="C22" s="166" t="s">
+      <c r="A22" s="158"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="167" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="157"/>
-      <c r="B23" s="172"/>
-      <c r="C23" s="166" t="s">
+      <c r="A23" s="158"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="167" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="98.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="157"/>
-      <c r="B24" s="172"/>
-      <c r="C24" s="163" t="s">
+      <c r="A24" s="158"/>
+      <c r="B24" s="173"/>
+      <c r="C24" s="164" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="157"/>
-      <c r="B25" s="172"/>
-      <c r="C25" s="158" t="s">
+      <c r="A25" s="158"/>
+      <c r="B25" s="173"/>
+      <c r="C25" s="159" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="157"/>
-      <c r="B26" s="172"/>
-      <c r="C26" s="167" t="s">
+      <c r="A26" s="158"/>
+      <c r="B26" s="173"/>
+      <c r="C26" s="168" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="157"/>
-      <c r="B27" s="172"/>
-      <c r="C27" s="168" t="s">
+      <c r="A27" s="158"/>
+      <c r="B27" s="173"/>
+      <c r="C27" s="169" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="159"/>
-      <c r="B28" s="173"/>
-      <c r="C28" s="169" t="s">
+      <c r="A28" s="160"/>
+      <c r="B28" s="174"/>
+      <c r="C28" s="170" t="s">
         <v>205</v>
       </c>
     </row>
@@ -28860,178 +29337,178 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABC9983-6AED-4B25-8AB6-C5125DB391F9}">
   <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="2" width="36.5" style="89" customWidth="1"/>
-    <col min="3" max="3" width="35.5" style="89" customWidth="1"/>
-    <col min="4" max="4" width="89.125" style="89" customWidth="1"/>
-    <col min="5" max="5" width="85.875" style="90" customWidth="1"/>
-    <col min="6" max="6" width="86.375" style="90" customWidth="1"/>
-    <col min="7" max="7" width="85.875" style="93" customWidth="1"/>
+    <col min="2" max="2" width="36.5" style="90" customWidth="1"/>
+    <col min="3" max="3" width="35.5" style="90" customWidth="1"/>
+    <col min="4" max="4" width="89.125" style="90" customWidth="1"/>
+    <col min="5" max="5" width="85.875" style="91" customWidth="1"/>
+    <col min="6" max="6" width="86.375" style="91" customWidth="1"/>
+    <col min="7" max="7" width="85.875" style="94" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="150.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="482" t="s">
+      <c r="B2" s="493" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="484" t="s">
+      <c r="C2" s="495" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="111" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="F2" s="112"/>
-      <c r="G2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="114"/>
     </row>
     <row r="3" spans="2:7" ht="176.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="483"/>
-      <c r="C3" s="485"/>
-      <c r="D3" s="114" t="s">
+      <c r="B3" s="494"/>
+      <c r="C3" s="496"/>
+      <c r="D3" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="114" t="s">
+      <c r="E3" s="115" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="115"/>
-      <c r="G3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="117"/>
     </row>
     <row r="4" spans="2:7" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="497" t="s">
+      <c r="B4" s="508" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="486" t="s">
+      <c r="C4" s="497" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="486"/>
-      <c r="E4" s="495" t="s">
+      <c r="D4" s="497"/>
+      <c r="E4" s="506" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="96" t="s">
+      <c r="G4" s="97" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="498"/>
-      <c r="C5" s="487"/>
-      <c r="D5" s="487"/>
-      <c r="E5" s="496"/>
-      <c r="F5" s="98" t="s">
+      <c r="B5" s="509"/>
+      <c r="C5" s="498"/>
+      <c r="D5" s="498"/>
+      <c r="E5" s="507"/>
+      <c r="F5" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="99" t="s">
+      <c r="G5" s="100" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="498"/>
-      <c r="C6" s="487" t="s">
+      <c r="B6" s="509"/>
+      <c r="C6" s="498" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="117" t="s">
+      <c r="E6" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="120"/>
     </row>
     <row r="7" spans="2:7" ht="155.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="498"/>
-      <c r="C7" s="487"/>
-      <c r="D7" s="97" t="s">
+      <c r="B7" s="509"/>
+      <c r="C7" s="498"/>
+      <c r="D7" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="E7" s="97" t="s">
+      <c r="E7" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="120"/>
-      <c r="G7" s="100"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="101"/>
     </row>
     <row r="8" spans="2:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="498"/>
-      <c r="C8" s="487"/>
-      <c r="D8" s="492" t="s">
+      <c r="B8" s="509"/>
+      <c r="C8" s="498"/>
+      <c r="D8" s="503" t="s">
         <v>242</v>
       </c>
-      <c r="E8" s="489" t="s">
+      <c r="E8" s="500" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="97" t="s">
+      <c r="F8" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="99" t="s">
+      <c r="G8" s="100" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="498"/>
-      <c r="C9" s="487"/>
-      <c r="D9" s="493"/>
-      <c r="E9" s="490"/>
-      <c r="F9" s="176" t="s">
+      <c r="B9" s="509"/>
+      <c r="C9" s="498"/>
+      <c r="D9" s="504"/>
+      <c r="E9" s="501"/>
+      <c r="F9" s="177" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="100" t="s">
+      <c r="G9" s="101" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="498"/>
-      <c r="C10" s="487"/>
-      <c r="D10" s="493"/>
-      <c r="E10" s="490"/>
-      <c r="F10" s="97" t="s">
+      <c r="B10" s="509"/>
+      <c r="C10" s="498"/>
+      <c r="D10" s="504"/>
+      <c r="E10" s="501"/>
+      <c r="F10" s="98" t="s">
         <v>237</v>
       </c>
-      <c r="G10" s="99" t="s">
+      <c r="G10" s="100" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="498"/>
-      <c r="C11" s="487"/>
-      <c r="D11" s="493"/>
-      <c r="E11" s="490"/>
-      <c r="F11" s="97" t="s">
+      <c r="B11" s="509"/>
+      <c r="C11" s="498"/>
+      <c r="D11" s="504"/>
+      <c r="E11" s="501"/>
+      <c r="F11" s="98" t="s">
         <v>235</v>
       </c>
-      <c r="G11" s="100" t="s">
+      <c r="G11" s="101" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="498"/>
-      <c r="C12" s="487"/>
-      <c r="D12" s="493"/>
-      <c r="E12" s="490"/>
-      <c r="F12" s="97" t="s">
+      <c r="B12" s="509"/>
+      <c r="C12" s="498"/>
+      <c r="D12" s="504"/>
+      <c r="E12" s="501"/>
+      <c r="F12" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="G12" s="100" t="s">
+      <c r="G12" s="101" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="499"/>
-      <c r="C13" s="488"/>
-      <c r="D13" s="494"/>
-      <c r="E13" s="491"/>
-      <c r="F13" s="101" t="s">
+      <c r="B13" s="510"/>
+      <c r="C13" s="499"/>
+      <c r="D13" s="505"/>
+      <c r="E13" s="502"/>
+      <c r="F13" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="102" t="s">
+      <c r="G13" s="103" t="s">
         <v>113</v>
       </c>
     </row>
@@ -29054,140 +29531,140 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04A566B-4D4D-4000-B483-895862B3A7F5}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5" style="177" customWidth="1"/>
-    <col min="2" max="2" width="83.375" style="177" customWidth="1"/>
-    <col min="3" max="3" width="63.625" style="177" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="177" customWidth="1"/>
-    <col min="5" max="5" width="84.125" style="177" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="177"/>
+    <col min="1" max="1" width="21.5" style="178" customWidth="1"/>
+    <col min="2" max="2" width="83.375" style="178" customWidth="1"/>
+    <col min="3" max="3" width="63.625" style="178" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="178" customWidth="1"/>
+    <col min="5" max="5" width="84.125" style="178" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="178"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="521" t="s">
+      <c r="B1" s="532" t="s">
         <v>243</v>
       </c>
-      <c r="C1" s="522"/>
-      <c r="D1" s="505" t="s">
+      <c r="C1" s="533"/>
+      <c r="D1" s="516" t="s">
         <v>247</v>
       </c>
-      <c r="E1" s="506"/>
+      <c r="E1" s="517"/>
     </row>
     <row r="2" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="179" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="523"/>
-      <c r="C2" s="523"/>
+      <c r="B2" s="534"/>
+      <c r="C2" s="534"/>
     </row>
     <row r="3" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="500" t="s">
+      <c r="A3" s="511" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="501" t="s">
+      <c r="B3" s="512" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="520"/>
-      <c r="D3" s="182" t="s">
+      <c r="C3" s="531"/>
+      <c r="D3" s="183" t="s">
         <v>266</v>
       </c>
-      <c r="E3" s="183"/>
+      <c r="E3" s="184"/>
     </row>
     <row r="4" spans="1:5" ht="383.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="500"/>
-      <c r="B4" s="194" t="s">
+      <c r="A4" s="511"/>
+      <c r="B4" s="195" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="196" t="s">
         <v>255</v>
       </c>
-      <c r="D4" s="184" t="s">
+      <c r="D4" s="185" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="185" t="s">
+      <c r="E4" s="186" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="500"/>
-      <c r="B5" s="501" t="s">
+      <c r="A5" s="511"/>
+      <c r="B5" s="512" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="513" t="s">
+      <c r="C5" s="524" t="s">
         <v>251</v>
       </c>
-      <c r="D5" s="518" t="s">
+      <c r="D5" s="529" t="s">
         <v>263</v>
       </c>
-      <c r="E5" s="516" t="s">
+      <c r="E5" s="527" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="500"/>
-      <c r="B6" s="502"/>
-      <c r="C6" s="514"/>
-      <c r="D6" s="519"/>
-      <c r="E6" s="517"/>
+      <c r="A6" s="511"/>
+      <c r="B6" s="513"/>
+      <c r="C6" s="525"/>
+      <c r="D6" s="530"/>
+      <c r="E6" s="528"/>
     </row>
     <row r="7" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="500"/>
-      <c r="B7" s="196" t="s">
+      <c r="A7" s="511"/>
+      <c r="B7" s="197" t="s">
         <v>258</v>
       </c>
-      <c r="C7" s="514"/>
-      <c r="D7" s="503" t="s">
+      <c r="C7" s="525"/>
+      <c r="D7" s="514" t="s">
         <v>256</v>
       </c>
-      <c r="E7" s="517"/>
+      <c r="E7" s="528"/>
     </row>
     <row r="8" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="500"/>
-      <c r="B8" s="197" t="s">
+      <c r="A8" s="511"/>
+      <c r="B8" s="198" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="515"/>
-      <c r="D8" s="504"/>
-      <c r="E8" s="510"/>
+      <c r="C8" s="526"/>
+      <c r="D8" s="515"/>
+      <c r="E8" s="521"/>
     </row>
     <row r="9" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="500"/>
-      <c r="B9" s="511" t="s">
+      <c r="A9" s="511"/>
+      <c r="B9" s="522" t="s">
         <v>246</v>
       </c>
-      <c r="C9" s="507"/>
-      <c r="D9" s="191" t="s">
+      <c r="C9" s="518"/>
+      <c r="D9" s="192" t="s">
         <v>264</v>
       </c>
-      <c r="E9" s="509" t="s">
+      <c r="E9" s="520" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="500"/>
-      <c r="B10" s="512"/>
-      <c r="C10" s="508"/>
-      <c r="D10" s="188" t="s">
+      <c r="A10" s="511"/>
+      <c r="B10" s="523"/>
+      <c r="C10" s="519"/>
+      <c r="D10" s="189" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="510"/>
+      <c r="E10" s="521"/>
     </row>
     <row r="11" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="500"/>
-      <c r="B11" s="189" t="s">
+      <c r="A11" s="511"/>
+      <c r="B11" s="190" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="190"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="187"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="188"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
-      <c r="B12" s="179"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -29210,122 +29687,122 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1739BFF5-83B2-4132-B96E-A009A87B2BE9}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5" style="177" customWidth="1"/>
-    <col min="2" max="2" width="80.625" style="177" customWidth="1"/>
-    <col min="3" max="3" width="100.625" style="177" customWidth="1"/>
-    <col min="4" max="5" width="80.625" style="177" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="177"/>
+    <col min="1" max="1" width="21.5" style="178" customWidth="1"/>
+    <col min="2" max="2" width="80.625" style="178" customWidth="1"/>
+    <col min="3" max="3" width="100.625" style="178" customWidth="1"/>
+    <col min="4" max="5" width="80.625" style="178" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="178"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="526" t="s">
+      <c r="B1" s="537" t="s">
         <v>249</v>
       </c>
-      <c r="C1" s="527"/>
-      <c r="D1" s="528" t="s">
+      <c r="C1" s="538"/>
+      <c r="D1" s="539" t="s">
         <v>248</v>
       </c>
-      <c r="E1" s="529"/>
+      <c r="E1" s="540"/>
     </row>
     <row r="2" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="500" t="s">
+      <c r="A2" s="511" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="199" t="s">
         <v>275</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="200" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="201" t="s">
+      <c r="D2" s="202" t="s">
         <v>272</v>
       </c>
-      <c r="E2" s="183"/>
+      <c r="E2" s="184"/>
     </row>
     <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="500"/>
-      <c r="B3" s="180" t="s">
+      <c r="A3" s="511"/>
+      <c r="B3" s="181" t="s">
         <v>260</v>
       </c>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="182" t="s">
         <v>250</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="185" t="s">
         <v>268</v>
       </c>
-      <c r="E3" s="185"/>
+      <c r="E3" s="186"/>
     </row>
     <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="500"/>
-      <c r="B4" s="200" t="s">
+      <c r="A4" s="511"/>
+      <c r="B4" s="201" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="211" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="188" t="s">
+      <c r="D4" s="189" t="s">
         <v>273</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="203" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="192"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="192"/>
+      <c r="E5" s="193"/>
     </row>
     <row r="6" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
-      <c r="B6" s="524" t="s">
+      <c r="A6" s="90"/>
+      <c r="B6" s="535" t="s">
         <v>280</v>
       </c>
-      <c r="C6" s="525"/>
-      <c r="D6" s="193"/>
-      <c r="E6" s="192"/>
+      <c r="C6" s="536"/>
+      <c r="D6" s="194"/>
+      <c r="E6" s="193"/>
     </row>
     <row r="7" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="500" t="s">
+      <c r="A7" s="511" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="204" t="s">
+      <c r="B7" s="205" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="203" t="s">
+      <c r="C7" s="204" t="s">
         <v>257</v>
       </c>
       <c r="D7" s="13"/>
-      <c r="E7" s="192"/>
+      <c r="E7" s="193"/>
     </row>
     <row r="8" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="500"/>
-      <c r="B8" s="205" t="s">
+      <c r="A8" s="511"/>
+      <c r="B8" s="206" t="s">
         <v>276</v>
       </c>
-      <c r="C8" s="206"/>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="500"/>
-      <c r="B9" s="207" t="s">
+      <c r="A9" s="511"/>
+      <c r="B9" s="208" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="209" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="500"/>
-      <c r="B10" s="209" t="s">
+      <c r="A10" s="511"/>
+      <c r="B10" s="210" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="211" t="s">
+      <c r="C10" s="212" t="s">
         <v>338</v>
       </c>
     </row>
@@ -29342,626 +29819,626 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A04174-2935-4E68-85E2-1D0814F4C678}">
   <dimension ref="A2:H57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="151" customWidth="1"/>
-    <col min="2" max="2" width="63.375" style="151" customWidth="1"/>
-    <col min="3" max="3" width="45.5" style="151" customWidth="1"/>
-    <col min="4" max="4" width="77.75" style="151" customWidth="1"/>
-    <col min="5" max="5" width="42.75" style="151" customWidth="1"/>
-    <col min="6" max="6" width="36.25" style="151" customWidth="1"/>
-    <col min="7" max="7" width="65.25" style="151" customWidth="1"/>
-    <col min="8" max="8" width="14.625" style="151" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="151"/>
+    <col min="1" max="1" width="13.375" style="152" customWidth="1"/>
+    <col min="2" max="2" width="63.375" style="152" customWidth="1"/>
+    <col min="3" max="3" width="45.5" style="152" customWidth="1"/>
+    <col min="4" max="4" width="77.75" style="152" customWidth="1"/>
+    <col min="5" max="5" width="42.75" style="152" customWidth="1"/>
+    <col min="6" max="6" width="36.25" style="152" customWidth="1"/>
+    <col min="7" max="7" width="65.25" style="152" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="152" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="152"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="315"/>
-      <c r="B2" s="315"/>
-      <c r="C2" s="315"/>
-      <c r="D2" s="315"/>
-      <c r="E2" s="315"/>
-      <c r="F2" s="315"/>
+      <c r="A2" s="305"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="305"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="315"/>
-      <c r="B3" s="315"/>
-      <c r="C3" s="315"/>
-      <c r="D3" s="315"/>
-      <c r="E3" s="315"/>
-      <c r="F3" s="315"/>
+      <c r="A3" s="305"/>
+      <c r="B3" s="305"/>
+      <c r="C3" s="305"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
     </row>
     <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="316"/>
-      <c r="B4" s="317"/>
-      <c r="C4" s="537" t="s">
+      <c r="A4" s="306"/>
+      <c r="B4" s="307"/>
+      <c r="C4" s="548" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="548"/>
+      <c r="E4" s="549"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="308" t="s">
+        <v>438</v>
+      </c>
+      <c r="H4" s="309"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="310"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="550" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="550"/>
+      <c r="E5" s="551"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="312" t="s">
+        <v>439</v>
+      </c>
+      <c r="H5" s="313" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="A6" s="310"/>
+      <c r="B6" s="314" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" s="315" t="s">
+        <v>442</v>
+      </c>
+      <c r="D6" s="316" t="s">
+        <v>443</v>
+      </c>
+      <c r="E6" s="317" t="s">
         <v>444</v>
       </c>
-      <c r="D4" s="537"/>
-      <c r="E4" s="538"/>
-      <c r="F4" s="315"/>
-      <c r="G4" s="318" t="s">
+      <c r="F6" s="305"/>
+      <c r="G6" s="312" t="s">
         <v>445</v>
       </c>
-      <c r="H4" s="319"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="320"/>
-      <c r="B5" s="321"/>
-      <c r="C5" s="539" t="s">
-        <v>445</v>
-      </c>
-      <c r="D5" s="539"/>
-      <c r="E5" s="540"/>
-      <c r="F5" s="315"/>
-      <c r="G5" s="322" t="s">
+      <c r="H6" s="318"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="310"/>
+      <c r="B7" s="311"/>
+      <c r="C7" s="319" t="s">
         <v>446</v>
       </c>
-      <c r="H5" s="323" t="s">
+      <c r="D7" s="311"/>
+      <c r="E7" s="320"/>
+      <c r="F7" s="305"/>
+      <c r="G7" s="321" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="320"/>
-      <c r="B6" s="324" t="s">
+      <c r="H7" s="322"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="310"/>
+      <c r="B8" s="323" t="s">
         <v>448</v>
       </c>
-      <c r="C6" s="325" t="s">
+      <c r="C8" s="324"/>
+      <c r="D8" s="311"/>
+      <c r="E8" s="320"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="542" t="s">
         <v>449</v>
       </c>
-      <c r="D6" s="326" t="s">
+      <c r="H8" s="543"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="310"/>
+      <c r="B9" s="325" t="s">
         <v>450</v>
       </c>
-      <c r="E6" s="327" t="s">
+      <c r="C9" s="326" t="s">
         <v>451</v>
       </c>
-      <c r="F6" s="315"/>
-      <c r="G6" s="322" t="s">
+      <c r="D9" s="311"/>
+      <c r="E9" s="320"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="544"/>
+      <c r="H9" s="545"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="327" t="s">
         <v>452</v>
       </c>
-      <c r="H6" s="328"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="320"/>
-      <c r="B7" s="321"/>
-      <c r="C7" s="329" t="s">
+      <c r="B10" s="311"/>
+      <c r="C10" s="328" t="s">
         <v>453</v>
       </c>
-      <c r="D7" s="321"/>
-      <c r="E7" s="330"/>
-      <c r="F7" s="315"/>
-      <c r="G7" s="331" t="s">
+      <c r="D10" s="329" t="s">
         <v>454</v>
       </c>
-      <c r="H7" s="332"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="320"/>
-      <c r="B8" s="333" t="s">
+      <c r="E10" s="320"/>
+      <c r="F10" s="305"/>
+      <c r="G10" s="544"/>
+      <c r="H10" s="545"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="310"/>
+      <c r="B11" s="324"/>
+      <c r="C11" s="326" t="s">
         <v>455</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="321"/>
-      <c r="E8" s="330"/>
-      <c r="F8" s="315"/>
-      <c r="G8" s="531" t="s">
+      <c r="D11" s="330" t="s">
         <v>456</v>
       </c>
-      <c r="H8" s="532"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="320"/>
-      <c r="B9" s="335" t="s">
+      <c r="E11" s="552" t="s">
         <v>457</v>
       </c>
-      <c r="C9" s="336" t="s">
+      <c r="F11" s="305"/>
+      <c r="G11" s="544"/>
+      <c r="H11" s="545"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="331"/>
+      <c r="B12" s="324"/>
+      <c r="C12" s="332" t="s">
         <v>458</v>
       </c>
-      <c r="D9" s="321"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="315"/>
-      <c r="G9" s="533"/>
-      <c r="H9" s="534"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="337" t="s">
+      <c r="D12" s="333" t="s">
         <v>459</v>
       </c>
-      <c r="B10" s="321"/>
-      <c r="C10" s="338" t="s">
+      <c r="E12" s="553"/>
+      <c r="G12" s="544"/>
+      <c r="H12" s="545"/>
+    </row>
+    <row r="13" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="331"/>
+      <c r="B13" s="334" t="s">
         <v>460</v>
       </c>
-      <c r="D10" s="339" t="s">
+      <c r="C13" s="335" t="s">
         <v>461</v>
       </c>
-      <c r="E10" s="330"/>
-      <c r="F10" s="315"/>
-      <c r="G10" s="533"/>
-      <c r="H10" s="534"/>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="320"/>
-      <c r="B11" s="334"/>
-      <c r="C11" s="336" t="s">
+      <c r="D13" s="336" t="s">
         <v>462</v>
       </c>
-      <c r="D11" s="340" t="s">
+      <c r="E13" s="554"/>
+      <c r="G13" s="544"/>
+      <c r="H13" s="545"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="331"/>
+      <c r="B14" s="337" t="s">
         <v>463</v>
       </c>
-      <c r="E11" s="541" t="s">
+      <c r="C14" s="338"/>
+      <c r="D14" s="339" t="s">
         <v>464</v>
       </c>
-      <c r="F11" s="315"/>
-      <c r="G11" s="533"/>
-      <c r="H11" s="534"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="341"/>
-      <c r="B12" s="334"/>
-      <c r="C12" s="342" t="s">
+      <c r="E14" s="340"/>
+      <c r="G14" s="544"/>
+      <c r="H14" s="545"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="331"/>
+      <c r="B15" s="337" t="s">
         <v>465</v>
       </c>
-      <c r="D12" s="343" t="s">
+      <c r="C15" s="341"/>
+      <c r="D15" s="342" t="s">
         <v>466</v>
       </c>
-      <c r="E12" s="542"/>
-      <c r="G12" s="533"/>
-      <c r="H12" s="534"/>
-    </row>
-    <row r="13" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="341"/>
-      <c r="B13" s="344" t="s">
+      <c r="E15" s="340"/>
+      <c r="G15" s="544"/>
+      <c r="H15" s="545"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="343"/>
+      <c r="B16" s="344" t="s">
         <v>467</v>
       </c>
-      <c r="C13" s="345" t="s">
+      <c r="C16" s="345"/>
+      <c r="D16" s="346" t="s">
         <v>468</v>
       </c>
-      <c r="D13" s="346" t="s">
+      <c r="E16" s="347"/>
+      <c r="G16" s="546"/>
+      <c r="H16" s="547"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="348"/>
+      <c r="B17" s="348"/>
+      <c r="C17" s="349"/>
+      <c r="D17" s="305"/>
+      <c r="G17" s="350"/>
+      <c r="H17" s="350"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="555" t="s">
         <v>469</v>
       </c>
-      <c r="E13" s="543"/>
-      <c r="G13" s="533"/>
-      <c r="H13" s="534"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="341"/>
-      <c r="B14" s="347" t="s">
+      <c r="B18" s="541"/>
+      <c r="C18" s="351"/>
+      <c r="D18" s="351"/>
+      <c r="E18" s="352"/>
+      <c r="G18" s="350"/>
+      <c r="H18" s="350"/>
+    </row>
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="541" t="s">
         <v>470</v>
       </c>
-      <c r="C14" s="348"/>
-      <c r="D14" s="349" t="s">
+      <c r="B19" s="541"/>
+      <c r="C19" s="351"/>
+      <c r="D19" s="351"/>
+      <c r="E19" s="353"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="541" t="s">
+        <v>466</v>
+      </c>
+      <c r="B20" s="541"/>
+      <c r="C20" s="351"/>
+      <c r="D20" s="354"/>
+      <c r="E20" s="353"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="541" t="s">
         <v>471</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="G14" s="533"/>
-      <c r="H14" s="534"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="341"/>
-      <c r="B15" s="347" t="s">
+      <c r="B21" s="541"/>
+      <c r="C21" s="355" t="s">
         <v>472</v>
       </c>
-      <c r="C15" s="351"/>
-      <c r="D15" s="352" t="s">
+      <c r="D21" s="354"/>
+      <c r="E21" s="353"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="351"/>
+      <c r="B22" s="351"/>
+      <c r="C22" s="354"/>
+      <c r="D22" s="354"/>
+      <c r="E22" s="353"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="354"/>
+      <c r="B23" s="354"/>
+      <c r="C23" s="356" t="s">
         <v>473</v>
       </c>
-      <c r="E15" s="350"/>
-      <c r="G15" s="533"/>
-      <c r="H15" s="534"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="353"/>
-      <c r="B16" s="354" t="s">
+      <c r="D23" s="560" t="s">
         <v>474</v>
       </c>
-      <c r="C16" s="355"/>
-      <c r="D16" s="356" t="s">
+      <c r="E23" s="561"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="354"/>
+      <c r="B24" s="355" t="s">
         <v>475</v>
       </c>
-      <c r="E16" s="357"/>
-      <c r="G16" s="535"/>
-      <c r="H16" s="536"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="358"/>
-      <c r="B17" s="358"/>
-      <c r="C17" s="359"/>
-      <c r="D17" s="315"/>
-      <c r="G17" s="360"/>
-      <c r="H17" s="360"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="544" t="s">
+      <c r="C24" s="357" t="s">
         <v>476</v>
       </c>
-      <c r="B18" s="530"/>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="362"/>
-      <c r="G18" s="360"/>
-      <c r="H18" s="360"/>
-    </row>
-    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="530" t="s">
+      <c r="D24" s="358" t="s">
         <v>477</v>
       </c>
-      <c r="B19" s="530"/>
-      <c r="C19" s="361"/>
-      <c r="D19" s="361"/>
-      <c r="E19" s="363"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="530" t="s">
+      <c r="E24" s="359"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="354"/>
+      <c r="B25" s="354"/>
+      <c r="C25" s="354"/>
+      <c r="D25" s="354"/>
+      <c r="E25" s="353"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="354"/>
+      <c r="B26" s="378" t="s">
         <v>473</v>
       </c>
-      <c r="B20" s="530"/>
-      <c r="C20" s="361"/>
-      <c r="D20" s="364"/>
-      <c r="E20" s="363"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="530" t="s">
+      <c r="C26" s="360" t="s">
         <v>478</v>
       </c>
-      <c r="B21" s="530"/>
-      <c r="C21" s="365" t="s">
+      <c r="D26" s="357" t="s">
         <v>479</v>
       </c>
-      <c r="D21" s="364"/>
-      <c r="E21" s="363"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="361"/>
-      <c r="B22" s="361"/>
-      <c r="C22" s="364"/>
-      <c r="D22" s="364"/>
-      <c r="E22" s="363"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="364"/>
-      <c r="B23" s="364"/>
-      <c r="C23" s="366" t="s">
+      <c r="E26" s="353"/>
+    </row>
+    <row r="27" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="354"/>
+      <c r="B27" s="354"/>
+      <c r="C27" s="361" t="s">
         <v>480</v>
       </c>
-      <c r="D23" s="549" t="s">
+      <c r="D27" s="354"/>
+      <c r="E27" s="353"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="562" t="s">
         <v>481</v>
       </c>
-      <c r="E23" s="550"/>
-    </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="364"/>
-      <c r="B24" s="365" t="s">
+      <c r="B28" s="562"/>
+      <c r="C28" s="362" t="s">
         <v>482</v>
       </c>
-      <c r="C24" s="367" t="s">
+      <c r="D28" s="354"/>
+      <c r="E28" s="353"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="354"/>
+      <c r="B29" s="354"/>
+      <c r="C29" s="363" t="s">
         <v>483</v>
       </c>
-      <c r="D24" s="368" t="s">
+      <c r="D29" s="364"/>
+      <c r="E29" s="353"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="354"/>
+      <c r="B30" s="354"/>
+      <c r="C30" s="364" t="s">
         <v>484</v>
       </c>
-      <c r="E24" s="369"/>
-    </row>
-    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="364"/>
-      <c r="B25" s="364"/>
-      <c r="C25" s="364"/>
-      <c r="D25" s="364"/>
-      <c r="E25" s="363"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="364"/>
-      <c r="B26" s="388" t="s">
-        <v>480</v>
-      </c>
-      <c r="C26" s="370" t="s">
+      <c r="D30" s="364" t="s">
+        <v>469</v>
+      </c>
+      <c r="E30" s="359"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="351"/>
+      <c r="B31" s="351"/>
+      <c r="C31" s="563" t="s">
         <v>485</v>
       </c>
-      <c r="D26" s="367" t="s">
+      <c r="D31" s="365" t="s">
         <v>486</v>
       </c>
-      <c r="E26" s="363"/>
-    </row>
-    <row r="27" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="364"/>
-      <c r="B27" s="364"/>
-      <c r="C27" s="371" t="s">
+      <c r="E31" s="366"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="351"/>
+      <c r="B32" s="351"/>
+      <c r="C32" s="563"/>
+      <c r="D32" s="364" t="s">
         <v>487</v>
       </c>
-      <c r="D27" s="364"/>
-      <c r="E27" s="363"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="551" t="s">
+      <c r="E32" s="359"/>
+    </row>
+    <row r="35" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="367" t="s">
         <v>488</v>
       </c>
-      <c r="B28" s="551"/>
-      <c r="C28" s="372" t="s">
+      <c r="C35" s="368"/>
+      <c r="D35" s="368"/>
+      <c r="E35" s="368"/>
+      <c r="F35" s="368"/>
+      <c r="G35" s="369"/>
+    </row>
+    <row r="36" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B36" s="370"/>
+      <c r="C36" s="354"/>
+      <c r="D36" s="354"/>
+      <c r="E36" s="354"/>
+      <c r="F36" s="354"/>
+      <c r="G36" s="371"/>
+    </row>
+    <row r="37" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B37" s="564" t="s">
         <v>489</v>
       </c>
-      <c r="D28" s="364"/>
-      <c r="E28" s="363"/>
-    </row>
-    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="364"/>
-      <c r="B29" s="364"/>
-      <c r="C29" s="373" t="s">
+      <c r="C37" s="354" t="s">
         <v>490</v>
       </c>
-      <c r="D29" s="374"/>
-      <c r="E29" s="363"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="364"/>
-      <c r="B30" s="364"/>
-      <c r="C30" s="374" t="s">
+      <c r="D37" s="354"/>
+      <c r="E37" s="354"/>
+      <c r="F37" s="354"/>
+      <c r="G37" s="371"/>
+    </row>
+    <row r="38" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="564"/>
+      <c r="C38" s="354" t="s">
         <v>491</v>
       </c>
-      <c r="D30" s="374" t="s">
-        <v>476</v>
-      </c>
-      <c r="E30" s="369"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="361"/>
-      <c r="B31" s="361"/>
-      <c r="C31" s="552" t="s">
+      <c r="D38" s="354"/>
+      <c r="E38" s="354"/>
+      <c r="F38" s="354"/>
+      <c r="G38" s="371"/>
+    </row>
+    <row r="39" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B39" s="370"/>
+      <c r="C39" s="354"/>
+      <c r="D39" s="354"/>
+      <c r="E39" s="354"/>
+      <c r="F39" s="354"/>
+      <c r="G39" s="371"/>
+    </row>
+    <row r="40" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B40" s="370"/>
+      <c r="C40" s="354"/>
+      <c r="D40" s="354"/>
+      <c r="E40" s="354"/>
+      <c r="F40" s="354"/>
+      <c r="G40" s="371"/>
+    </row>
+    <row r="41" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B41" s="565" t="s">
         <v>492</v>
       </c>
-      <c r="D31" s="375" t="s">
+      <c r="C41" s="354" t="s">
         <v>493</v>
       </c>
-      <c r="E31" s="376"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="361"/>
-      <c r="B32" s="361"/>
-      <c r="C32" s="552"/>
-      <c r="D32" s="374" t="s">
+      <c r="D41" s="354"/>
+      <c r="E41" s="354"/>
+      <c r="F41" s="354"/>
+      <c r="G41" s="371"/>
+    </row>
+    <row r="42" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B42" s="565"/>
+      <c r="C42" s="354" t="s">
         <v>494</v>
       </c>
-      <c r="E32" s="369"/>
-    </row>
-    <row r="35" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B35" s="377" t="s">
+      <c r="D42" s="354"/>
+      <c r="E42" s="354"/>
+      <c r="F42" s="354"/>
+      <c r="G42" s="371"/>
+    </row>
+    <row r="43" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B43" s="565"/>
+      <c r="C43" s="354" t="s">
         <v>495</v>
       </c>
-      <c r="C35" s="378"/>
-      <c r="D35" s="378"/>
-      <c r="E35" s="378"/>
-      <c r="F35" s="378"/>
-      <c r="G35" s="379"/>
-    </row>
-    <row r="36" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B36" s="380"/>
-      <c r="C36" s="364"/>
-      <c r="D36" s="364"/>
-      <c r="E36" s="364"/>
-      <c r="F36" s="364"/>
-      <c r="G36" s="381"/>
-    </row>
-    <row r="37" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B37" s="553" t="s">
+      <c r="D43" s="354"/>
+      <c r="E43" s="354"/>
+      <c r="F43" s="354"/>
+      <c r="G43" s="371"/>
+    </row>
+    <row r="44" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" s="370"/>
+      <c r="C44" s="354"/>
+      <c r="D44" s="354"/>
+      <c r="E44" s="354"/>
+      <c r="F44" s="354"/>
+      <c r="G44" s="371"/>
+    </row>
+    <row r="45" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B45" s="565" t="s">
         <v>496</v>
       </c>
-      <c r="C37" s="364" t="s">
+      <c r="C45" s="354" t="s">
         <v>497</v>
       </c>
-      <c r="D37" s="364"/>
-      <c r="E37" s="364"/>
-      <c r="F37" s="364"/>
-      <c r="G37" s="381"/>
-    </row>
-    <row r="38" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B38" s="553"/>
-      <c r="C38" s="364" t="s">
+      <c r="D45" s="373" t="s">
         <v>498</v>
       </c>
-      <c r="D38" s="364"/>
-      <c r="E38" s="364"/>
-      <c r="F38" s="364"/>
-      <c r="G38" s="381"/>
-    </row>
-    <row r="39" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B39" s="380"/>
-      <c r="C39" s="364"/>
-      <c r="D39" s="364"/>
-      <c r="E39" s="364"/>
-      <c r="F39" s="364"/>
-      <c r="G39" s="381"/>
-    </row>
-    <row r="40" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B40" s="380"/>
-      <c r="C40" s="364"/>
-      <c r="D40" s="364"/>
-      <c r="E40" s="364"/>
-      <c r="F40" s="364"/>
-      <c r="G40" s="381"/>
-    </row>
-    <row r="41" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B41" s="554" t="s">
+      <c r="E45" s="354"/>
+      <c r="F45" s="354"/>
+      <c r="G45" s="371"/>
+    </row>
+    <row r="46" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B46" s="565"/>
+      <c r="C46" s="556" t="s">
         <v>499</v>
       </c>
-      <c r="C41" s="364" t="s">
+      <c r="D46" s="566" t="s">
+        <v>469</v>
+      </c>
+      <c r="E46" s="354" t="s">
+        <v>470</v>
+      </c>
+      <c r="F46" s="354"/>
+      <c r="G46" s="371"/>
+    </row>
+    <row r="47" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B47" s="565"/>
+      <c r="C47" s="556"/>
+      <c r="D47" s="566"/>
+      <c r="E47" s="556" t="s">
+        <v>466</v>
+      </c>
+      <c r="F47" s="354" t="s">
         <v>500</v>
       </c>
-      <c r="D41" s="364"/>
-      <c r="E41" s="364"/>
-      <c r="F41" s="364"/>
-      <c r="G41" s="381"/>
-    </row>
-    <row r="42" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B42" s="554"/>
-      <c r="C42" s="364" t="s">
+      <c r="G47" s="371"/>
+    </row>
+    <row r="48" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B48" s="565"/>
+      <c r="C48" s="556"/>
+      <c r="D48" s="566"/>
+      <c r="E48" s="556"/>
+      <c r="F48" s="354" t="s">
         <v>501</v>
       </c>
-      <c r="D42" s="364"/>
-      <c r="E42" s="364"/>
-      <c r="F42" s="364"/>
-      <c r="G42" s="381"/>
-    </row>
-    <row r="43" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B43" s="554"/>
-      <c r="C43" s="364" t="s">
+      <c r="G48" s="371"/>
+    </row>
+    <row r="49" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B49" s="565"/>
+      <c r="C49" s="556"/>
+      <c r="D49" s="566"/>
+      <c r="E49" s="354" t="s">
+        <v>471</v>
+      </c>
+      <c r="F49" s="354"/>
+      <c r="G49" s="371"/>
+    </row>
+    <row r="50" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B50" s="370"/>
+      <c r="C50" s="354"/>
+      <c r="D50" s="354"/>
+      <c r="E50" s="354"/>
+      <c r="F50" s="354"/>
+      <c r="G50" s="371"/>
+    </row>
+    <row r="51" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B51" s="370"/>
+      <c r="C51" s="354"/>
+      <c r="D51" s="354"/>
+      <c r="E51" s="354"/>
+      <c r="F51" s="354"/>
+      <c r="G51" s="371"/>
+    </row>
+    <row r="52" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B52" s="370"/>
+      <c r="C52" s="354"/>
+      <c r="D52" s="354"/>
+      <c r="E52" s="354"/>
+      <c r="F52" s="354"/>
+      <c r="G52" s="371"/>
+    </row>
+    <row r="53" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B53" s="370"/>
+      <c r="C53" s="354"/>
+      <c r="D53" s="354"/>
+      <c r="E53" s="354"/>
+      <c r="F53" s="354"/>
+      <c r="G53" s="371"/>
+    </row>
+    <row r="54" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B54" s="372" t="s">
         <v>502</v>
       </c>
-      <c r="D43" s="364"/>
-      <c r="E43" s="364"/>
-      <c r="F43" s="364"/>
-      <c r="G43" s="381"/>
-    </row>
-    <row r="44" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B44" s="380"/>
-      <c r="C44" s="364"/>
-      <c r="D44" s="364"/>
-      <c r="E44" s="364"/>
-      <c r="F44" s="364"/>
-      <c r="G44" s="381"/>
-    </row>
-    <row r="45" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B45" s="554" t="s">
+      <c r="C54" s="354" t="s">
         <v>503</v>
       </c>
-      <c r="C45" s="364" t="s">
+      <c r="D54" s="354" t="s">
+        <v>469</v>
+      </c>
+      <c r="E54" s="354"/>
+      <c r="F54" s="354"/>
+      <c r="G54" s="371"/>
+    </row>
+    <row r="55" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B55" s="372"/>
+      <c r="C55" s="556" t="s">
         <v>504</v>
       </c>
-      <c r="D45" s="383" t="s">
+      <c r="D55" s="558" t="s">
+        <v>483</v>
+      </c>
+      <c r="E55" s="354" t="s">
         <v>505</v>
       </c>
-      <c r="E45" s="364"/>
-      <c r="F45" s="364"/>
-      <c r="G45" s="381"/>
-    </row>
-    <row r="46" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B46" s="554"/>
-      <c r="C46" s="545" t="s">
-        <v>506</v>
-      </c>
-      <c r="D46" s="555" t="s">
-        <v>476</v>
-      </c>
-      <c r="E46" s="364" t="s">
-        <v>477</v>
-      </c>
-      <c r="F46" s="364"/>
-      <c r="G46" s="381"/>
-    </row>
-    <row r="47" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B47" s="554"/>
-      <c r="C47" s="545"/>
-      <c r="D47" s="555"/>
-      <c r="E47" s="545" t="s">
-        <v>473</v>
-      </c>
-      <c r="F47" s="364" t="s">
-        <v>507</v>
-      </c>
-      <c r="G47" s="381"/>
-    </row>
-    <row r="48" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B48" s="554"/>
-      <c r="C48" s="545"/>
-      <c r="D48" s="555"/>
-      <c r="E48" s="545"/>
-      <c r="F48" s="364" t="s">
-        <v>508</v>
-      </c>
-      <c r="G48" s="381"/>
-    </row>
-    <row r="49" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B49" s="554"/>
-      <c r="C49" s="545"/>
-      <c r="D49" s="555"/>
-      <c r="E49" s="364" t="s">
-        <v>478</v>
-      </c>
-      <c r="F49" s="364"/>
-      <c r="G49" s="381"/>
-    </row>
-    <row r="50" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B50" s="380"/>
-      <c r="C50" s="364"/>
-      <c r="D50" s="364"/>
-      <c r="E50" s="364"/>
-      <c r="F50" s="364"/>
-      <c r="G50" s="381"/>
-    </row>
-    <row r="51" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B51" s="380"/>
-      <c r="C51" s="364"/>
-      <c r="D51" s="364"/>
-      <c r="E51" s="364"/>
-      <c r="F51" s="364"/>
-      <c r="G51" s="381"/>
-    </row>
-    <row r="52" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B52" s="380"/>
-      <c r="C52" s="364"/>
-      <c r="D52" s="364"/>
-      <c r="E52" s="364"/>
-      <c r="F52" s="364"/>
-      <c r="G52" s="381"/>
-    </row>
-    <row r="53" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B53" s="380"/>
-      <c r="C53" s="364"/>
-      <c r="D53" s="364"/>
-      <c r="E53" s="364"/>
-      <c r="F53" s="364"/>
-      <c r="G53" s="381"/>
-    </row>
-    <row r="54" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B54" s="382" t="s">
-        <v>509</v>
-      </c>
-      <c r="C54" s="364" t="s">
-        <v>510</v>
-      </c>
-      <c r="D54" s="364" t="s">
-        <v>476</v>
-      </c>
-      <c r="E54" s="364"/>
-      <c r="F54" s="364"/>
-      <c r="G54" s="381"/>
-    </row>
-    <row r="55" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B55" s="382"/>
-      <c r="C55" s="545" t="s">
-        <v>511</v>
-      </c>
-      <c r="D55" s="547" t="s">
-        <v>490</v>
-      </c>
-      <c r="E55" s="364" t="s">
-        <v>512</v>
-      </c>
-      <c r="F55" s="364"/>
-      <c r="G55" s="381"/>
+      <c r="F55" s="354"/>
+      <c r="G55" s="371"/>
     </row>
     <row r="56" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B56" s="382"/>
-      <c r="C56" s="545"/>
-      <c r="D56" s="547"/>
-      <c r="E56" s="545" t="s">
+      <c r="B56" s="372"/>
+      <c r="C56" s="556"/>
+      <c r="D56" s="558"/>
+      <c r="E56" s="556" t="s">
+        <v>485</v>
+      </c>
+      <c r="F56" s="374" t="s">
+        <v>486</v>
+      </c>
+      <c r="G56" s="371"/>
+    </row>
+    <row r="57" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B57" s="375"/>
+      <c r="C57" s="557"/>
+      <c r="D57" s="559"/>
+      <c r="E57" s="557"/>
+      <c r="F57" s="376" t="s">
+        <v>487</v>
+      </c>
+      <c r="G57" s="377" t="s">
         <v>492</v>
-      </c>
-      <c r="F56" s="384" t="s">
-        <v>493</v>
-      </c>
-      <c r="G56" s="381"/>
-    </row>
-    <row r="57" spans="2:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B57" s="385"/>
-      <c r="C57" s="546"/>
-      <c r="D57" s="548"/>
-      <c r="E57" s="546"/>
-      <c r="F57" s="386" t="s">
-        <v>494</v>
-      </c>
-      <c r="G57" s="387" t="s">
-        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -29993,7 +30470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FFC8A31-2954-4D5E-8C71-06508C680CF7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -30004,109 +30481,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="140.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="215" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="218" t="s">
+      <c r="B1" s="219" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="219" t="s">
+      <c r="C1" s="220" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="221" t="s">
+      <c r="B2" s="222" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="219" t="s">
+      <c r="C2" s="220" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="222" t="s">
+      <c r="A5" s="223" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="223" t="s">
+      <c r="A6" s="224" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="232" t="s">
         <v>320</v>
       </c>
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="238" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="225" t="s">
+      <c r="A8" s="226" t="s">
         <v>321</v>
       </c>
-      <c r="B8" s="235" t="s">
+      <c r="B8" s="236" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="233" t="s">
+      <c r="A9" s="234" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="228" t="s">
+      <c r="B9" s="229" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="140.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="234" t="s">
+      <c r="A10" s="235" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="236" t="s">
+      <c r="B10" s="237" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="223" t="s">
+      <c r="A11" s="224" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="231" t="s">
+      <c r="A12" s="232" t="s">
         <v>327</v>
       </c>
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="238" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="238" t="s">
+      <c r="A13" s="239" t="s">
         <v>328</v>
       </c>
-      <c r="B13" s="239"/>
+      <c r="B13" s="240"/>
     </row>
     <row r="14" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="243" t="s">
+      <c r="A14" s="244" t="s">
         <v>329</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="242" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="240" t="s">
+      <c r="A15" s="241" t="s">
         <v>330</v>
       </c>
-      <c r="B15" s="244" t="s">
+      <c r="B15" s="245" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="242" t="s">
+      <c r="A16" s="243" t="s">
         <v>331</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="246" t="s">
         <v>336</v>
       </c>
     </row>
@@ -30116,166 +30593,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FD2E74-B274-41E9-9104-FF7D6F240A1C}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="103.375" style="212" customWidth="1"/>
-    <col min="2" max="2" width="124.375" style="213" customWidth="1"/>
-    <col min="3" max="3" width="84.5" style="212" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="212"/>
+    <col min="1" max="1" width="103.375" style="213" customWidth="1"/>
+    <col min="2" max="2" width="124.375" style="214" customWidth="1"/>
+    <col min="3" max="3" width="84.5" style="213" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="213"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="83.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="215" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="218" t="s">
+      <c r="B1" s="219" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="210" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="216" t="s">
         <v>313</v>
       </c>
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="220" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="214" t="s">
+      <c r="A3" s="215" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="219" t="s">
+      <c r="B3" s="220" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="135.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="215" t="s">
+      <c r="A4" s="216" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="220" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="216" t="s">
+      <c r="A5" s="217" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="220" t="s">
+      <c r="B5" s="221" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="219" t="s">
+      <c r="C5" s="220" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="217" t="s">
+      <c r="A6" s="218" t="s">
         <v>283</v>
       </c>
-      <c r="B6" s="221" t="s">
+      <c r="B6" s="222" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="220" t="s">
+      <c r="C6" s="221" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="222" t="s">
+      <c r="A8" s="223" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="223" t="s">
+      <c r="A9" s="224" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="225" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="246" t="s">
+      <c r="A11" s="247" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="246" t="s">
+      <c r="B11" s="247" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="223" t="s">
+      <c r="A12" s="224" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="225" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="225" t="s">
+      <c r="A14" s="226" t="s">
         <v>299</v>
       </c>
-      <c r="B14" s="225" t="s">
+      <c r="B14" s="226" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="226" t="s">
+      <c r="A15" s="227" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="226"/>
+      <c r="B15" s="227"/>
     </row>
     <row r="16" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="232" t="s">
+      <c r="A16" s="233" t="s">
         <v>294</v>
       </c>
-      <c r="B16" s="228" t="s">
+      <c r="B16" s="229" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="226" t="s">
+      <c r="A17" s="227" t="s">
         <v>295</v>
       </c>
-      <c r="B17" s="228" t="s">
+      <c r="B17" s="229" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="226" t="s">
+      <c r="A18" s="227" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="228" t="s">
+      <c r="B18" s="229" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="226" t="s">
+      <c r="A19" s="227" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="228" t="s">
+      <c r="B19" s="229" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="230" t="s">
+      <c r="C19" s="231" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="226" t="s">
+      <c r="A20" s="227" t="s">
         <v>298</v>
       </c>
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="234" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="227" t="s">
+      <c r="A21" s="228" t="s">
         <v>311</v>
       </c>
-      <c r="B21" s="229" t="s">
+      <c r="B21" s="230" t="s">
         <v>310</v>
       </c>
     </row>
@@ -30285,14 +30762,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006E31C4-CD31-48CA-B81E-5FFC6A54C896}">
-  <dimension ref="A3:E26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A3:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.75" style="47" customWidth="1"/>
-    <col min="2" max="2" width="23" style="389" customWidth="1"/>
-    <col min="3" max="3" width="30.75" style="390" customWidth="1"/>
+    <col min="2" max="2" width="23" style="379" customWidth="1"/>
+    <col min="3" max="3" width="30.75" style="380" customWidth="1"/>
     <col min="4" max="4" width="111.125" style="47" customWidth="1"/>
     <col min="5" max="5" width="123.5" style="47" customWidth="1"/>
     <col min="6" max="16384" width="9" style="47"/>
@@ -30300,163 +30777,153 @@
   <sheetData>
     <row r="3" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="B3" s="379" t="s">
+        <v>506</v>
+      </c>
+      <c r="C3" s="380" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="381" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="379" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="379" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="379" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="C10" s="382" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" s="383" t="s">
+        <v>527</v>
+      </c>
+      <c r="E10" s="283" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="C11" s="382" t="s">
+        <v>518</v>
+      </c>
+      <c r="D11" s="384" t="s">
+        <v>526</v>
+      </c>
+      <c r="E11" s="381" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="C12" s="382" t="s">
+        <v>519</v>
+      </c>
+      <c r="D12" s="384" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="114" x14ac:dyDescent="0.2">
+      <c r="B13" s="567" t="s">
+        <v>521</v>
+      </c>
+      <c r="C13" s="382" t="s">
         <v>522</v>
       </c>
-      <c r="B3" s="389" t="s">
+      <c r="D13" s="384" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="B14" s="567"/>
+      <c r="C14" s="382" t="s">
+        <v>541</v>
+      </c>
+      <c r="D14" s="384" t="s">
+        <v>542</v>
+      </c>
+      <c r="E14" s="381" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="C15" s="382" t="s">
+        <v>536</v>
+      </c>
+      <c r="D15" s="384" t="s">
+        <v>537</v>
+      </c>
+      <c r="E15" s="283" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="C16" s="382" t="s">
+        <v>528</v>
+      </c>
+      <c r="D16" s="384" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="C17" s="382" t="s">
+        <v>530</v>
+      </c>
+      <c r="D17" s="384" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="C18" s="382" t="s">
+        <v>532</v>
+      </c>
+      <c r="D18" s="384" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="C19" s="382" t="s">
+        <v>534</v>
+      </c>
+      <c r="D19" s="384" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="C20" s="382" t="s">
+        <v>539</v>
+      </c>
+      <c r="D20" s="384" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="B21" s="379" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="379" t="s">
         <v>513</v>
       </c>
-      <c r="C3" s="390" t="s">
-        <v>517</v>
-      </c>
-      <c r="D3" s="391" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="389" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="379" t="s">
         <v>514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="389" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="389" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="185.25" x14ac:dyDescent="0.2">
-      <c r="C10" s="392" t="s">
-        <v>523</v>
-      </c>
-      <c r="D10" s="393" t="s">
-        <v>534</v>
-      </c>
-      <c r="E10" s="293" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="C11" s="392" t="s">
-        <v>525</v>
-      </c>
-      <c r="D11" s="394" t="s">
-        <v>533</v>
-      </c>
-      <c r="E11" s="391" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="C12" s="392" t="s">
-        <v>526</v>
-      </c>
-      <c r="D12" s="394" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="114" x14ac:dyDescent="0.2">
-      <c r="B13" s="556" t="s">
-        <v>528</v>
-      </c>
-      <c r="C13" s="392" t="s">
-        <v>529</v>
-      </c>
-      <c r="D13" s="394" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="B14" s="556"/>
-      <c r="C14" s="392" t="s">
-        <v>548</v>
-      </c>
-      <c r="D14" s="394" t="s">
-        <v>549</v>
-      </c>
-      <c r="E14" s="391" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="C15" s="392" t="s">
-        <v>543</v>
-      </c>
-      <c r="D15" s="394" t="s">
-        <v>544</v>
-      </c>
-      <c r="E15" s="293" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="C16" s="392" t="s">
-        <v>535</v>
-      </c>
-      <c r="D16" s="394" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="213.75" x14ac:dyDescent="0.2">
-      <c r="C17" s="392" t="s">
-        <v>537</v>
-      </c>
-      <c r="D17" s="394" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="C18" s="392" t="s">
-        <v>539</v>
-      </c>
-      <c r="D18" s="394" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="C19" s="392" t="s">
-        <v>541</v>
-      </c>
-      <c r="D19" s="394" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="C20" s="392" t="s">
-        <v>546</v>
-      </c>
-      <c r="D20" s="394" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D21" s="293"/>
-    </row>
-    <row r="22" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="47" t="s">
-        <v>518</v>
-      </c>
-      <c r="B22" s="389" t="s">
-        <v>519</v>
-      </c>
-      <c r="C22" s="392" t="s">
-        <v>551</v>
-      </c>
-      <c r="D22" s="394" t="s">
-        <v>552</v>
-      </c>
-      <c r="E22" s="293"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="389" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="389" t="s">
-        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -30478,74 +30945,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="413" t="s">
+      <c r="B3" s="425" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="87" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="415"/>
-      <c r="C4" s="86" t="s">
+      <c r="B4" s="427"/>
+      <c r="C4" s="87" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="87"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="413" t="s">
+      <c r="B6" s="425" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="87" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="414"/>
-      <c r="C7" s="86" t="s">
+      <c r="B7" s="426"/>
+      <c r="C7" s="87" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="414"/>
-      <c r="C8" s="86" t="s">
+      <c r="B8" s="426"/>
+      <c r="C8" s="87" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="415"/>
-      <c r="C9" s="86" t="s">
+      <c r="B9" s="427"/>
+      <c r="C9" s="87" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="87"/>
+      <c r="C10" s="88"/>
     </row>
     <row r="11" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="87"/>
+      <c r="C11" s="88"/>
     </row>
     <row r="12" spans="2:3" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="416" t="s">
+      <c r="B12" s="428" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="89" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="417"/>
-      <c r="C13" s="88" t="s">
+      <c r="B13" s="429"/>
+      <c r="C13" s="89" t="s">
         <v>100</v>
       </c>
     </row>
@@ -30553,17 +31020,17 @@
       <c r="B14" s="20"/>
     </row>
     <row r="15" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="76" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="76" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="76" t="s">
         <v>53</v>
       </c>
     </row>
@@ -30580,8 +31047,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E613E84-5728-4A95-A233-D47632953345}">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.875" style="14" customWidth="1"/>
     <col min="2" max="2" width="61.75" style="14" customWidth="1"/>
@@ -30592,334 +31059,205 @@
     <col min="7" max="7" width="96.75" style="14" customWidth="1"/>
     <col min="8" max="8" width="76.625" style="14" customWidth="1"/>
     <col min="9" max="9" width="61.5" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="14"/>
+    <col min="10" max="15" width="9" style="14"/>
+    <col min="16" max="17" width="54" style="14" customWidth="1"/>
+    <col min="18" max="18" width="74.625" style="14" customWidth="1"/>
+    <col min="19" max="19" width="44.125" style="14" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="66" x14ac:dyDescent="0.2">
-      <c r="A1" s="421" t="s">
+    <row r="1" spans="1:9" ht="219.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="433" t="s">
+        <v>549</v>
+      </c>
+      <c r="B1" s="435" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1" s="441" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1" s="254" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="255" t="s">
+        <v>370</v>
+      </c>
+      <c r="F1" s="256"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="257"/>
+    </row>
+    <row r="2" spans="1:9" ht="234.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="433"/>
+      <c r="B2" s="435"/>
+      <c r="C2" s="442"/>
+      <c r="D2" s="440" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="258" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="258" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" s="259"/>
+      <c r="H2" s="260"/>
+    </row>
+    <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="433"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="442"/>
+      <c r="D3" s="440"/>
+      <c r="E3" s="261" t="s">
+        <v>374</v>
+      </c>
+      <c r="F3" s="258" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="259"/>
+      <c r="H3" s="262"/>
+    </row>
+    <row r="4" spans="1:9" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="433"/>
+      <c r="B4" s="435"/>
+      <c r="C4" s="442"/>
+      <c r="D4" s="440"/>
+      <c r="E4" s="261" t="s">
+        <v>375</v>
+      </c>
+      <c r="F4" s="258" t="s">
+        <v>373</v>
+      </c>
+      <c r="G4" s="259"/>
+      <c r="H4" s="262"/>
+    </row>
+    <row r="5" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="433"/>
+      <c r="B5" s="435"/>
+      <c r="C5" s="442"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="261" t="s">
+        <v>379</v>
+      </c>
+      <c r="F5" s="258" t="s">
+        <v>381</v>
+      </c>
+      <c r="G5" s="259"/>
+      <c r="H5" s="262"/>
+    </row>
+    <row r="6" spans="1:9" ht="219.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="433"/>
+      <c r="B6" s="435"/>
+      <c r="C6" s="442"/>
+      <c r="D6" s="440"/>
+      <c r="E6" s="258" t="s">
+        <v>376</v>
+      </c>
+      <c r="F6" s="261"/>
+      <c r="G6" s="259"/>
+      <c r="H6" s="262"/>
+    </row>
+    <row r="7" spans="1:9" ht="200.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="433"/>
+      <c r="B7" s="435"/>
+      <c r="C7" s="442"/>
+      <c r="D7" s="263" t="s">
+        <v>377</v>
+      </c>
+      <c r="E7" s="263"/>
+      <c r="F7" s="259"/>
+      <c r="G7" s="259"/>
+      <c r="H7" s="260"/>
+    </row>
+    <row r="8" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="434"/>
+      <c r="B8" s="436"/>
+      <c r="C8" s="264" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="265"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="265"/>
+      <c r="G8" s="265"/>
+      <c r="H8" s="266"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="434"/>
+      <c r="B9" s="432" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="423" t="s">
-        <v>367</v>
-      </c>
-      <c r="C1" s="432" t="s">
-        <v>366</v>
-      </c>
-      <c r="D1" s="426" t="s">
-        <v>368</v>
-      </c>
-      <c r="E1" s="253" t="s">
-        <v>370</v>
-      </c>
-      <c r="F1" s="253" t="s">
+      <c r="C9" s="437" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="105"/>
+    </row>
+    <row r="10" spans="1:9" ht="240" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="434"/>
+      <c r="B10" s="432"/>
+      <c r="C10" s="438"/>
+      <c r="D10" s="430" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="430" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="106"/>
+      <c r="I10" s="108"/>
+    </row>
+    <row r="11" spans="1:9" ht="123" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="434"/>
+      <c r="B11" s="432"/>
+      <c r="C11" s="439"/>
+      <c r="D11" s="431"/>
+      <c r="E11" s="431"/>
+      <c r="F11" s="253" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="109" t="s">
+        <v>382</v>
+      </c>
+      <c r="H11" s="253" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="110" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="140.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="434"/>
+      <c r="B12" s="267" t="s">
         <v>372</v>
       </c>
-      <c r="G1" s="254"/>
-      <c r="H1" s="255"/>
-    </row>
-    <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="421"/>
-      <c r="B2" s="423"/>
-      <c r="C2" s="433"/>
-      <c r="D2" s="427"/>
-      <c r="E2" s="256" t="s">
-        <v>369</v>
-      </c>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-    </row>
-    <row r="3" spans="1:8" ht="106.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="421"/>
-      <c r="B3" s="423"/>
-      <c r="C3" s="433"/>
-      <c r="D3" s="428" t="s">
-        <v>386</v>
-      </c>
-      <c r="E3" s="248" t="s">
-        <v>389</v>
-      </c>
-      <c r="F3" s="249"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250"/>
-    </row>
-    <row r="4" spans="1:8" ht="250.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="421"/>
-      <c r="B4" s="423"/>
-      <c r="C4" s="433"/>
-      <c r="D4" s="428"/>
-      <c r="E4" s="248" t="s">
-        <v>390</v>
-      </c>
-      <c r="F4" s="251" t="s">
-        <v>391</v>
-      </c>
-      <c r="G4" s="249"/>
-      <c r="H4" s="250"/>
-    </row>
-    <row r="5" spans="1:8" ht="156" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="423"/>
-      <c r="C5" s="433"/>
-      <c r="D5" s="428" t="s">
-        <v>392</v>
-      </c>
-      <c r="E5" s="248" t="s">
-        <v>401</v>
-      </c>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="250"/>
-    </row>
-    <row r="6" spans="1:8" ht="156" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="423"/>
-      <c r="C6" s="433"/>
-      <c r="D6" s="428"/>
-      <c r="E6" s="248" t="s">
-        <v>399</v>
-      </c>
-      <c r="F6" s="251" t="s">
-        <v>400</v>
-      </c>
-      <c r="G6" s="249"/>
-      <c r="H6" s="250"/>
-    </row>
-    <row r="7" spans="1:8" ht="156" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="423"/>
-      <c r="C7" s="433"/>
-      <c r="D7" s="428"/>
-      <c r="E7" s="248" t="s">
-        <v>398</v>
-      </c>
-      <c r="F7" s="251" t="s">
-        <v>393</v>
-      </c>
-      <c r="G7" s="249"/>
-      <c r="H7" s="250"/>
-    </row>
-    <row r="8" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="423"/>
-      <c r="C8" s="433"/>
-      <c r="D8" s="428" t="s">
-        <v>394</v>
-      </c>
-      <c r="E8" s="252" t="s">
-        <v>396</v>
-      </c>
-      <c r="F8" s="251"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="250"/>
-    </row>
-    <row r="9" spans="1:8" ht="204.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="421"/>
-      <c r="B9" s="423"/>
-      <c r="C9" s="434"/>
-      <c r="D9" s="438"/>
-      <c r="E9" s="259" t="s">
-        <v>395</v>
-      </c>
-      <c r="F9" s="260" t="s">
-        <v>397</v>
-      </c>
-      <c r="G9" s="261"/>
-      <c r="H9" s="262"/>
-    </row>
-    <row r="10" spans="1:8" ht="235.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="424"/>
-      <c r="C10" s="436" t="s">
-        <v>373</v>
-      </c>
-      <c r="D10" s="264" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="265" t="s">
-        <v>376</v>
-      </c>
-      <c r="F10" s="266"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="267"/>
-    </row>
-    <row r="11" spans="1:8" ht="234.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="424"/>
-      <c r="C11" s="437"/>
-      <c r="D11" s="435" t="s">
-        <v>375</v>
-      </c>
-      <c r="E11" s="268" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="268" t="s">
-        <v>384</v>
-      </c>
-      <c r="G11" s="269"/>
-      <c r="H11" s="270"/>
-    </row>
-    <row r="12" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="424"/>
-      <c r="C12" s="437"/>
-      <c r="D12" s="435"/>
-      <c r="E12" s="271" t="s">
-        <v>380</v>
-      </c>
-      <c r="F12" s="268" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="269"/>
-      <c r="H12" s="272"/>
-    </row>
-    <row r="13" spans="1:8" ht="201" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="421"/>
-      <c r="B13" s="424"/>
-      <c r="C13" s="437"/>
-      <c r="D13" s="435"/>
-      <c r="E13" s="271" t="s">
-        <v>381</v>
-      </c>
-      <c r="F13" s="268" t="s">
-        <v>379</v>
-      </c>
-      <c r="G13" s="269"/>
-      <c r="H13" s="272"/>
-    </row>
-    <row r="14" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="421"/>
-      <c r="B14" s="424"/>
-      <c r="C14" s="437"/>
-      <c r="D14" s="435"/>
-      <c r="E14" s="271" t="s">
-        <v>385</v>
-      </c>
-      <c r="F14" s="268" t="s">
-        <v>387</v>
-      </c>
-      <c r="G14" s="269"/>
-      <c r="H14" s="272"/>
-    </row>
-    <row r="15" spans="1:8" ht="265.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="421"/>
-      <c r="B15" s="424"/>
-      <c r="C15" s="437"/>
-      <c r="D15" s="435"/>
-      <c r="E15" s="268" t="s">
-        <v>382</v>
-      </c>
-      <c r="F15" s="271"/>
-      <c r="G15" s="269"/>
-      <c r="H15" s="272"/>
-    </row>
-    <row r="16" spans="1:8" ht="222.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="421"/>
-      <c r="B16" s="424"/>
-      <c r="C16" s="437"/>
-      <c r="D16" s="273" t="s">
-        <v>383</v>
-      </c>
-      <c r="E16" s="273"/>
-      <c r="F16" s="269"/>
-      <c r="G16" s="269"/>
-      <c r="H16" s="270"/>
-    </row>
-    <row r="17" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="422"/>
-      <c r="B17" s="425"/>
-      <c r="C17" s="274" t="s">
-        <v>374</v>
-      </c>
-      <c r="D17" s="275"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="275"/>
-      <c r="G17" s="275"/>
-      <c r="H17" s="276"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="422"/>
-      <c r="B18" s="420" t="s">
-        <v>377</v>
-      </c>
-      <c r="C18" s="429" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="103" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="104"/>
-    </row>
-    <row r="19" spans="1:9" ht="264.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="422"/>
-      <c r="B19" s="420"/>
-      <c r="C19" s="430"/>
-      <c r="D19" s="418" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="418" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="106" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="105"/>
-      <c r="I19" s="107"/>
-    </row>
-    <row r="20" spans="1:9" ht="123" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="422"/>
-      <c r="B20" s="420"/>
-      <c r="C20" s="431"/>
-      <c r="D20" s="419"/>
-      <c r="E20" s="419"/>
-      <c r="F20" s="263" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="108" t="s">
-        <v>388</v>
-      </c>
-      <c r="H20" s="263" t="s">
-        <v>63</v>
-      </c>
-      <c r="I20" s="109" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="162.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="422"/>
-      <c r="B21" s="277" t="s">
-        <v>378</v>
-      </c>
-      <c r="C21" s="278"/>
-      <c r="D21" s="278"/>
-      <c r="E21" s="278"/>
-      <c r="F21" s="278"/>
-      <c r="G21" s="278"/>
-      <c r="H21" s="278"/>
-      <c r="I21" s="279"/>
+      <c r="C12" s="268"/>
+      <c r="D12" s="268"/>
+      <c r="E12" s="268"/>
+      <c r="F12" s="268"/>
+      <c r="G12" s="268"/>
+      <c r="H12" s="268"/>
+      <c r="I12" s="269"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="A1:A21"/>
-    <mergeCell ref="B1:B17"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="C1:C9"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D19:D20"/>
+  <mergeCells count="8">
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A1:A12"/>
+    <mergeCell ref="B1:B8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="C1:C7"/>
+    <mergeCell ref="D10:D11"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30927,6 +31265,196 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B52F92-A913-4D8C-921C-23C3531BFE0E}">
+  <dimension ref="B1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="40.375" customWidth="1"/>
+    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="4" max="4" width="79.375" customWidth="1"/>
+    <col min="5" max="5" width="89.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="447" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1" s="443" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="251" t="s">
+        <v>544</v>
+      </c>
+      <c r="E1" s="390" t="s">
+        <v>548</v>
+      </c>
+      <c r="F1" s="386"/>
+    </row>
+    <row r="2" spans="2:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="448"/>
+      <c r="C2" s="444"/>
+      <c r="D2" s="394" t="s">
+        <v>545</v>
+      </c>
+      <c r="E2" s="395"/>
+      <c r="F2" s="396"/>
+    </row>
+    <row r="3" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="448"/>
+      <c r="C3" s="445"/>
+      <c r="D3" s="252" t="s">
+        <v>546</v>
+      </c>
+      <c r="E3" s="397" t="s">
+        <v>547</v>
+      </c>
+      <c r="F3" s="387"/>
+    </row>
+    <row r="4" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="448"/>
+      <c r="C4" s="446" t="s">
+        <v>380</v>
+      </c>
+      <c r="D4" s="249" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" s="391"/>
+      <c r="F4" s="388"/>
+    </row>
+    <row r="5" spans="2:6" ht="240" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="448"/>
+      <c r="C5" s="446"/>
+      <c r="D5" s="249" t="s">
+        <v>384</v>
+      </c>
+      <c r="E5" s="392" t="s">
+        <v>385</v>
+      </c>
+      <c r="F5" s="388"/>
+    </row>
+    <row r="6" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="448"/>
+      <c r="C6" s="446" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" s="249" t="s">
+        <v>395</v>
+      </c>
+      <c r="E6" s="391"/>
+      <c r="F6" s="388"/>
+    </row>
+    <row r="7" spans="2:6" ht="140.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="448"/>
+      <c r="C7" s="446"/>
+      <c r="D7" s="249" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" s="392" t="s">
+        <v>394</v>
+      </c>
+      <c r="F7" s="388"/>
+    </row>
+    <row r="8" spans="2:6" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="448"/>
+      <c r="C8" s="446"/>
+      <c r="D8" s="249" t="s">
+        <v>392</v>
+      </c>
+      <c r="E8" s="392" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="388"/>
+    </row>
+    <row r="9" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="448"/>
+      <c r="C9" s="446" t="s">
+        <v>388</v>
+      </c>
+      <c r="D9" s="250" t="s">
+        <v>390</v>
+      </c>
+      <c r="E9" s="392"/>
+      <c r="F9" s="388"/>
+    </row>
+    <row r="10" spans="2:6" ht="408" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="449"/>
+      <c r="C10" s="450"/>
+      <c r="D10" s="385" t="s">
+        <v>389</v>
+      </c>
+      <c r="E10" s="393" t="s">
+        <v>391</v>
+      </c>
+      <c r="F10" s="389"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B1:B10"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5792C1A0-F828-4FA1-90EB-50ED88734389}">
+  <dimension ref="B5:D11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="60.625" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="50.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="399" t="s">
+        <v>552</v>
+      </c>
+      <c r="D5" s="405" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B6" s="400" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B7" s="398" t="s">
+        <v>554</v>
+      </c>
+      <c r="D7" s="404" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="403" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="401" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="402" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D232CB-C49D-45B0-951E-55C71D1ABED0}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -30938,10 +31466,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="440" t="s">
+      <c r="A2" s="452" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="442" t="s">
+      <c r="B2" s="454" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="22" t="s">
@@ -30958,16 +31486,16 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="441"/>
-      <c r="B3" s="443"/>
+      <c r="A3" s="453"/>
+      <c r="B3" s="455"/>
       <c r="C3" s="37"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
       <c r="F3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="441"/>
-      <c r="B4" s="443" t="s">
+      <c r="A4" s="453"/>
+      <c r="B4" s="455" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="28" t="s">
@@ -30984,8 +31512,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="441"/>
-      <c r="B5" s="443"/>
+      <c r="A5" s="453"/>
+      <c r="B5" s="455"/>
       <c r="C5" s="32" t="s">
         <v>39</v>
       </c>
@@ -30994,11 +31522,11 @@
       <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="441" t="s">
+      <c r="A6" s="453" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="443" t="s">
-        <v>414</v>
+      <c r="B6" s="455" t="s">
+        <v>407</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>43</v>
@@ -31012,16 +31540,16 @@
       <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="441"/>
-      <c r="B7" s="443"/>
+      <c r="A7" s="453"/>
+      <c r="B7" s="455"/>
       <c r="C7" s="37"/>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
       <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="441"/>
-      <c r="B8" s="443" t="s">
+      <c r="A8" s="453"/>
+      <c r="B8" s="455" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="28" t="s">
@@ -31036,40 +31564,40 @@
       <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="444"/>
-      <c r="B9" s="445"/>
-      <c r="C9" s="289" t="s">
+      <c r="A9" s="456"/>
+      <c r="B9" s="457"/>
+      <c r="C9" s="279" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="290"/>
+      <c r="D9" s="280"/>
       <c r="E9" s="35"/>
       <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="285" t="s">
-        <v>413</v>
-      </c>
-      <c r="B10" s="287" t="s">
-        <v>418</v>
-      </c>
-      <c r="C10" s="291" t="s">
-        <v>417</v>
-      </c>
-      <c r="D10" s="292" t="s">
-        <v>415</v>
-      </c>
-      <c r="E10" s="288" t="s">
-        <v>416</v>
-      </c>
-      <c r="F10" s="286" t="s">
+      <c r="A10" s="275" t="s">
+        <v>406</v>
+      </c>
+      <c r="B10" s="277" t="s">
+        <v>411</v>
+      </c>
+      <c r="C10" s="281" t="s">
+        <v>410</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>408</v>
+      </c>
+      <c r="E10" s="278" t="s">
+        <v>409</v>
+      </c>
+      <c r="F10" s="276" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C11" s="439" t="s">
-        <v>419</v>
-      </c>
-      <c r="D11" s="439"/>
+      <c r="C11" s="451" t="s">
+        <v>412</v>
+      </c>
+      <c r="D11" s="451"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -31086,7 +31614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86808304-4150-4C1C-BB7E-BB6AAF8EC7CC}">
   <dimension ref="B2:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -31101,19 +31629,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B2" s="448" t="s">
+      <c r="B2" s="460" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="449"/>
-      <c r="D2" s="449"/>
-      <c r="E2" s="449"/>
-      <c r="F2" s="450"/>
+      <c r="C2" s="461"/>
+      <c r="D2" s="461"/>
+      <c r="E2" s="461"/>
+      <c r="F2" s="462"/>
     </row>
     <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="59" t="s">
         <v>70</v>
       </c>
       <c r="D3" s="48"/>
@@ -31124,7 +31652,7 @@
     </row>
     <row r="4" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="49"/>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="66" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="48"/>
@@ -31152,7 +31680,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="66"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="51" t="s">
         <v>68</v>
       </c>
@@ -31163,121 +31691,119 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="68" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="D8" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="63" t="s">
+      <c r="E8" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="64" t="s">
+      <c r="F8" s="65" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B9" s="84"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="61" t="s">
+      <c r="B9" s="85"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="78"/>
-      <c r="F9" s="69"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="10" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B10" s="446" t="s">
+      <c r="B10" s="458" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="447"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="69"/>
+      <c r="C10" s="459"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="70"/>
     </row>
     <row r="11" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="83"/>
-      <c r="C11" s="68" t="s">
+      <c r="B11" s="84"/>
+      <c r="C11" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="76"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="69"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="70"/>
     </row>
     <row r="12" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="82"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="77" t="s">
+      <c r="B12" s="83"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="80"/>
-      <c r="F12" s="69"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="70"/>
     </row>
     <row r="13" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="73"/>
+      <c r="B13" s="74"/>
       <c r="C13" s="54"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="68" t="s">
+      <c r="D13" s="73"/>
+      <c r="E13" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="73"/>
-      <c r="C14" s="558" t="s">
-        <v>553</v>
-      </c>
+      <c r="B14" s="74"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="54"/>
-      <c r="E14" s="72"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="56"/>
     </row>
     <row r="15" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="73"/>
-      <c r="C15" s="557" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="58" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="54"/>
       <c r="E15" s="55"/>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="60" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B16" s="73"/>
-      <c r="C16" s="557" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="58" t="s">
         <v>75</v>
       </c>
       <c r="D16" s="54"/>
       <c r="E16" s="55"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="71"/>
     </row>
     <row r="17" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B17" s="73"/>
-      <c r="C17" s="60" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="61" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="55"/>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="61" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B18" s="73"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="54"/>
-      <c r="D18" s="60" t="s">
+      <c r="D18" s="61" t="s">
         <v>85</v>
       </c>
       <c r="E18" s="55"/>
       <c r="F18" s="54"/>
     </row>
     <row r="19" spans="2:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B19" s="73"/>
+      <c r="B19" s="74"/>
       <c r="C19" s="54"/>
       <c r="D19" s="54"/>
-      <c r="E19" s="71" t="s">
+      <c r="E19" s="72" t="s">
         <v>86</v>
       </c>
       <c r="F19" s="54"/>
@@ -31289,410 +31815,409 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{170671FC-7126-4F53-9577-31F7E194AC02}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.625" style="129" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="129" customWidth="1"/>
-    <col min="3" max="3" width="68.375" style="129" customWidth="1"/>
-    <col min="4" max="4" width="84.625" style="129" customWidth="1"/>
-    <col min="5" max="5" width="42.25" style="129" customWidth="1"/>
-    <col min="6" max="6" width="69" style="131" customWidth="1"/>
-    <col min="7" max="7" width="41.5" style="130" customWidth="1"/>
-    <col min="8" max="8" width="44.625" style="130" customWidth="1"/>
-    <col min="9" max="9" width="43.5" style="130" customWidth="1"/>
-    <col min="10" max="10" width="41.625" style="130" customWidth="1"/>
-    <col min="11" max="11" width="37.5" style="130" customWidth="1"/>
-    <col min="12" max="12" width="56.25" style="130" customWidth="1"/>
+    <col min="1" max="1" width="57.625" style="130" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="130" customWidth="1"/>
+    <col min="3" max="3" width="68.375" style="130" customWidth="1"/>
+    <col min="4" max="4" width="84.625" style="130" customWidth="1"/>
+    <col min="5" max="5" width="42.25" style="130" customWidth="1"/>
+    <col min="6" max="6" width="69" style="132" customWidth="1"/>
+    <col min="7" max="7" width="41.5" style="131" customWidth="1"/>
+    <col min="8" max="8" width="44.625" style="131" customWidth="1"/>
+    <col min="9" max="9" width="43.5" style="131" customWidth="1"/>
+    <col min="10" max="10" width="41.625" style="131" customWidth="1"/>
+    <col min="11" max="11" width="37.5" style="131" customWidth="1"/>
+    <col min="12" max="12" width="56.25" style="131" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="131" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="130" t="s">
+      <c r="A3" s="131" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="467" t="s">
+      <c r="A4" s="479" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="468" t="s">
+      <c r="B4" s="480" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="469" t="s">
+      <c r="C4" s="481" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="133" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="141" t="s">
+      <c r="E4" s="142" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="142"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="134"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="135"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="467"/>
-      <c r="B5" s="468"/>
-      <c r="C5" s="470"/>
-      <c r="D5" s="138" t="s">
+      <c r="A5" s="479"/>
+      <c r="B5" s="480"/>
+      <c r="C5" s="482"/>
+      <c r="D5" s="139" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="143" t="s">
+      <c r="E5" s="144" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="144" t="s">
+      <c r="F5" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="138" t="s">
+      <c r="G5" s="139" t="s">
         <v>179</v>
       </c>
-      <c r="H5" s="145" t="s">
+      <c r="H5" s="146" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="467"/>
-      <c r="B6" s="467" t="s">
+      <c r="A6" s="479"/>
+      <c r="B6" s="479" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="474" t="s">
+      <c r="C6" s="486" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="474" t="s">
+      <c r="D6" s="486" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="474" t="s">
+      <c r="E6" s="486" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="471" t="s">
+      <c r="F6" s="483" t="s">
         <v>157</v>
       </c>
-      <c r="G6" s="132" t="s">
+      <c r="G6" s="133" t="s">
         <v>158</v>
       </c>
-      <c r="H6" s="133" t="s">
+      <c r="H6" s="134" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="134"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="135"/>
     </row>
     <row r="7" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="467"/>
-      <c r="B7" s="467"/>
-      <c r="C7" s="474"/>
-      <c r="D7" s="474"/>
-      <c r="E7" s="474"/>
-      <c r="F7" s="472"/>
-      <c r="G7" s="460" t="s">
+      <c r="A7" s="479"/>
+      <c r="B7" s="479"/>
+      <c r="C7" s="486"/>
+      <c r="D7" s="486"/>
+      <c r="E7" s="486"/>
+      <c r="F7" s="484"/>
+      <c r="G7" s="472" t="s">
         <v>159</v>
       </c>
-      <c r="H7" s="460" t="s">
+      <c r="H7" s="472" t="s">
         <v>175</v>
       </c>
-      <c r="I7" s="462" t="s">
+      <c r="I7" s="474" t="s">
         <v>160</v>
       </c>
-      <c r="J7" s="460" t="s">
+      <c r="J7" s="472" t="s">
         <v>151</v>
       </c>
-      <c r="K7" s="135" t="s">
+      <c r="K7" s="136" t="s">
         <v>161</v>
       </c>
-      <c r="L7" s="136" t="s">
+      <c r="L7" s="137" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="467"/>
-      <c r="B8" s="467"/>
-      <c r="C8" s="474"/>
-      <c r="D8" s="474"/>
-      <c r="E8" s="474"/>
-      <c r="F8" s="472"/>
-      <c r="G8" s="460"/>
-      <c r="H8" s="460"/>
-      <c r="I8" s="462"/>
-      <c r="J8" s="460"/>
-      <c r="K8" s="135" t="s">
+      <c r="A8" s="479"/>
+      <c r="B8" s="479"/>
+      <c r="C8" s="486"/>
+      <c r="D8" s="486"/>
+      <c r="E8" s="486"/>
+      <c r="F8" s="484"/>
+      <c r="G8" s="472"/>
+      <c r="H8" s="472"/>
+      <c r="I8" s="474"/>
+      <c r="J8" s="472"/>
+      <c r="K8" s="136" t="s">
         <v>162</v>
       </c>
-      <c r="L8" s="137" t="s">
+      <c r="L8" s="138" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="467"/>
-      <c r="B9" s="467"/>
-      <c r="C9" s="474"/>
-      <c r="D9" s="474"/>
-      <c r="E9" s="474"/>
-      <c r="F9" s="472"/>
-      <c r="G9" s="460"/>
-      <c r="H9" s="460"/>
-      <c r="I9" s="462"/>
-      <c r="J9" s="135" t="s">
+      <c r="A9" s="479"/>
+      <c r="B9" s="479"/>
+      <c r="C9" s="486"/>
+      <c r="D9" s="486"/>
+      <c r="E9" s="486"/>
+      <c r="F9" s="484"/>
+      <c r="G9" s="472"/>
+      <c r="H9" s="472"/>
+      <c r="I9" s="474"/>
+      <c r="J9" s="136" t="s">
         <v>152</v>
       </c>
-      <c r="K9" s="135"/>
-      <c r="L9" s="137" t="s">
+      <c r="K9" s="136"/>
+      <c r="L9" s="138" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="467"/>
-      <c r="B10" s="467"/>
-      <c r="C10" s="474"/>
-      <c r="D10" s="474"/>
-      <c r="E10" s="474"/>
-      <c r="F10" s="472"/>
-      <c r="G10" s="460"/>
-      <c r="H10" s="461" t="s">
+      <c r="A10" s="479"/>
+      <c r="B10" s="479"/>
+      <c r="C10" s="486"/>
+      <c r="D10" s="486"/>
+      <c r="E10" s="486"/>
+      <c r="F10" s="484"/>
+      <c r="G10" s="472"/>
+      <c r="H10" s="473" t="s">
         <v>163</v>
       </c>
-      <c r="I10" s="461" t="s">
+      <c r="I10" s="473" t="s">
         <v>165</v>
       </c>
-      <c r="J10" s="465"/>
-      <c r="K10" s="135" t="s">
+      <c r="J10" s="477"/>
+      <c r="K10" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="136" t="s">
+      <c r="L10" s="137" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="467"/>
-      <c r="B11" s="467"/>
-      <c r="C11" s="474"/>
-      <c r="D11" s="474"/>
-      <c r="E11" s="474"/>
-      <c r="F11" s="472"/>
-      <c r="G11" s="460"/>
-      <c r="H11" s="463"/>
-      <c r="I11" s="464"/>
-      <c r="J11" s="466"/>
-      <c r="K11" s="135" t="s">
+      <c r="A11" s="479"/>
+      <c r="B11" s="479"/>
+      <c r="C11" s="486"/>
+      <c r="D11" s="486"/>
+      <c r="E11" s="486"/>
+      <c r="F11" s="484"/>
+      <c r="G11" s="472"/>
+      <c r="H11" s="475"/>
+      <c r="I11" s="476"/>
+      <c r="J11" s="478"/>
+      <c r="K11" s="136" t="s">
         <v>169</v>
       </c>
-      <c r="L11" s="140" t="s">
+      <c r="L11" s="141" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="467"/>
-      <c r="B12" s="467"/>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="473"/>
-      <c r="G12" s="461"/>
-      <c r="H12" s="463"/>
-      <c r="I12" s="139" t="s">
+      <c r="A12" s="479"/>
+      <c r="B12" s="479"/>
+      <c r="C12" s="486"/>
+      <c r="D12" s="486"/>
+      <c r="E12" s="486"/>
+      <c r="F12" s="485"/>
+      <c r="G12" s="473"/>
+      <c r="H12" s="475"/>
+      <c r="I12" s="140" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="466"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="147" t="s">
+      <c r="J12" s="478"/>
+      <c r="K12" s="140"/>
+      <c r="L12" s="148" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="467"/>
-      <c r="B13" s="467"/>
-      <c r="C13" s="474" t="s">
+      <c r="A13" s="479"/>
+      <c r="B13" s="479"/>
+      <c r="C13" s="486" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="475" t="s">
+      <c r="D13" s="487" t="s">
         <v>184</v>
       </c>
-      <c r="E13" s="457" t="s">
+      <c r="E13" s="469" t="s">
         <v>191</v>
       </c>
-      <c r="F13" s="457" t="s">
+      <c r="F13" s="469" t="s">
         <v>188</v>
       </c>
-      <c r="G13" s="457" t="s">
+      <c r="G13" s="469" t="s">
         <v>187</v>
       </c>
-      <c r="H13" s="457" t="s">
+      <c r="H13" s="469" t="s">
         <v>189</v>
       </c>
-      <c r="I13" s="148" t="s">
+      <c r="I13" s="149" t="s">
         <v>193</v>
       </c>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-      <c r="L13" s="150"/>
+      <c r="J13" s="150"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="151"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="467"/>
-      <c r="B14" s="467"/>
-      <c r="C14" s="474"/>
-      <c r="D14" s="476"/>
-      <c r="E14" s="453"/>
-      <c r="F14" s="453"/>
-      <c r="G14" s="453"/>
-      <c r="H14" s="453"/>
-      <c r="I14" s="453" t="s">
+      <c r="A14" s="479"/>
+      <c r="B14" s="479"/>
+      <c r="C14" s="486"/>
+      <c r="D14" s="488"/>
+      <c r="E14" s="465"/>
+      <c r="F14" s="465"/>
+      <c r="G14" s="465"/>
+      <c r="H14" s="465"/>
+      <c r="I14" s="465" t="s">
         <v>190</v>
       </c>
-      <c r="J14" s="453" t="s">
+      <c r="J14" s="465" t="s">
         <v>194</v>
       </c>
-      <c r="K14" s="453" t="s">
+      <c r="K14" s="465" t="s">
         <v>199</v>
       </c>
-      <c r="L14" s="452" t="s">
+      <c r="L14" s="464" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="467"/>
-      <c r="B15" s="467"/>
-      <c r="C15" s="474"/>
-      <c r="D15" s="476"/>
-      <c r="E15" s="453"/>
-      <c r="F15" s="453"/>
-      <c r="G15" s="453"/>
-      <c r="H15" s="453"/>
-      <c r="I15" s="453"/>
-      <c r="J15" s="453"/>
-      <c r="K15" s="453"/>
-      <c r="L15" s="452"/>
+      <c r="A15" s="479"/>
+      <c r="B15" s="479"/>
+      <c r="C15" s="486"/>
+      <c r="D15" s="488"/>
+      <c r="E15" s="465"/>
+      <c r="F15" s="465"/>
+      <c r="G15" s="465"/>
+      <c r="H15" s="465"/>
+      <c r="I15" s="465"/>
+      <c r="J15" s="465"/>
+      <c r="K15" s="465"/>
+      <c r="L15" s="464"/>
     </row>
     <row r="16" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="467"/>
-      <c r="B16" s="467"/>
-      <c r="C16" s="474"/>
-      <c r="D16" s="476"/>
-      <c r="E16" s="453"/>
-      <c r="F16" s="453"/>
-      <c r="G16" s="453"/>
-      <c r="H16" s="453"/>
-      <c r="I16" s="453"/>
-      <c r="J16" s="453" t="s">
+      <c r="A16" s="479"/>
+      <c r="B16" s="479"/>
+      <c r="C16" s="486"/>
+      <c r="D16" s="488"/>
+      <c r="E16" s="465"/>
+      <c r="F16" s="465"/>
+      <c r="G16" s="465"/>
+      <c r="H16" s="465"/>
+      <c r="I16" s="465"/>
+      <c r="J16" s="465" t="s">
         <v>195</v>
       </c>
-      <c r="K16" s="453"/>
-      <c r="L16" s="451" t="s">
+      <c r="K16" s="465"/>
+      <c r="L16" s="463" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="467"/>
-      <c r="B17" s="467"/>
-      <c r="C17" s="474"/>
-      <c r="D17" s="476"/>
-      <c r="E17" s="453"/>
-      <c r="F17" s="453"/>
-      <c r="G17" s="453"/>
-      <c r="H17" s="453"/>
-      <c r="I17" s="453"/>
-      <c r="J17" s="453"/>
-      <c r="K17" s="453"/>
-      <c r="L17" s="451"/>
+      <c r="A17" s="479"/>
+      <c r="B17" s="479"/>
+      <c r="C17" s="486"/>
+      <c r="D17" s="488"/>
+      <c r="E17" s="465"/>
+      <c r="F17" s="465"/>
+      <c r="G17" s="465"/>
+      <c r="H17" s="465"/>
+      <c r="I17" s="465"/>
+      <c r="J17" s="465"/>
+      <c r="K17" s="465"/>
+      <c r="L17" s="463"/>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="467"/>
-      <c r="B18" s="467"/>
-      <c r="C18" s="474"/>
-      <c r="D18" s="476"/>
-      <c r="E18" s="453" t="s">
+      <c r="A18" s="479"/>
+      <c r="B18" s="479"/>
+      <c r="C18" s="486"/>
+      <c r="D18" s="488"/>
+      <c r="E18" s="465" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="458" t="s">
+      <c r="F18" s="470" t="s">
         <v>204</v>
       </c>
-      <c r="G18" s="453" t="s">
+      <c r="G18" s="465" t="s">
         <v>186</v>
       </c>
-      <c r="H18" s="453"/>
-      <c r="I18" s="458" t="s">
+      <c r="H18" s="465"/>
+      <c r="I18" s="470" t="s">
         <v>202</v>
       </c>
-      <c r="J18" s="453" t="s">
+      <c r="J18" s="465" t="s">
         <v>196</v>
       </c>
-      <c r="K18" s="453" t="s">
+      <c r="K18" s="465" t="s">
         <v>198</v>
       </c>
-      <c r="L18" s="455" t="s">
+      <c r="L18" s="467" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="467"/>
-      <c r="B19" s="467"/>
-      <c r="C19" s="474"/>
-      <c r="D19" s="476"/>
-      <c r="E19" s="453"/>
-      <c r="F19" s="458"/>
-      <c r="G19" s="453"/>
-      <c r="H19" s="453"/>
-      <c r="I19" s="458"/>
-      <c r="J19" s="453"/>
-      <c r="K19" s="453"/>
-      <c r="L19" s="455"/>
+      <c r="A19" s="479"/>
+      <c r="B19" s="479"/>
+      <c r="C19" s="486"/>
+      <c r="D19" s="488"/>
+      <c r="E19" s="465"/>
+      <c r="F19" s="470"/>
+      <c r="G19" s="465"/>
+      <c r="H19" s="465"/>
+      <c r="I19" s="470"/>
+      <c r="J19" s="465"/>
+      <c r="K19" s="465"/>
+      <c r="L19" s="467"/>
     </row>
     <row r="20" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="467"/>
-      <c r="B20" s="467"/>
-      <c r="C20" s="474"/>
-      <c r="D20" s="476"/>
-      <c r="E20" s="453"/>
-      <c r="F20" s="458"/>
-      <c r="G20" s="453"/>
-      <c r="H20" s="453"/>
-      <c r="I20" s="458"/>
-      <c r="J20" s="453" t="s">
+      <c r="A20" s="479"/>
+      <c r="B20" s="479"/>
+      <c r="C20" s="486"/>
+      <c r="D20" s="488"/>
+      <c r="E20" s="465"/>
+      <c r="F20" s="470"/>
+      <c r="G20" s="465"/>
+      <c r="H20" s="465"/>
+      <c r="I20" s="470"/>
+      <c r="J20" s="465" t="s">
         <v>197</v>
       </c>
-      <c r="K20" s="453"/>
-      <c r="L20" s="451" t="s">
+      <c r="K20" s="465"/>
+      <c r="L20" s="463" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="467"/>
-      <c r="B21" s="467"/>
-      <c r="C21" s="474"/>
-      <c r="D21" s="477"/>
-      <c r="E21" s="454"/>
-      <c r="F21" s="459"/>
-      <c r="G21" s="454"/>
-      <c r="H21" s="454"/>
-      <c r="I21" s="459"/>
-      <c r="J21" s="454"/>
-      <c r="K21" s="454"/>
-      <c r="L21" s="456"/>
+      <c r="A21" s="479"/>
+      <c r="B21" s="479"/>
+      <c r="C21" s="486"/>
+      <c r="D21" s="489"/>
+      <c r="E21" s="466"/>
+      <c r="F21" s="471"/>
+      <c r="G21" s="466"/>
+      <c r="H21" s="466"/>
+      <c r="I21" s="471"/>
+      <c r="J21" s="466"/>
+      <c r="K21" s="466"/>
+      <c r="L21" s="468"/>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="146"/>
+      <c r="C25" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -31739,7 +32264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1315223-EA03-458B-929B-BCBCA8DFEC8C}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -31749,33 +32274,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="99.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="127" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="128" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="47" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="284" t="s">
-        <v>409</v>
-      </c>
-      <c r="B2" s="125"/>
+      <c r="A2" s="274" t="s">
+        <v>403</v>
+      </c>
+      <c r="B2" s="126"/>
     </row>
     <row r="3" spans="1:2" ht="264" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="273" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="122" t="s">
-        <v>407</v>
-      </c>
-      <c r="B4" s="123" t="s">
-        <v>408</v>
+      <c r="A4" s="123" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" s="124" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31791,19 +32316,19 @@
       <c r="B6" s="8"/>
     </row>
     <row r="7" spans="1:2" s="47" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="284" t="s">
-        <v>410</v>
-      </c>
-      <c r="B7" s="128" t="s">
+      <c r="A7" s="274" t="s">
+        <v>404</v>
+      </c>
+      <c r="B7" s="129" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="124" t="s">
-        <v>411</v>
-      </c>
-      <c r="B8" s="124" t="s">
-        <v>412</v>
+      <c r="A8" s="125" t="s">
+        <v>405</v>
+      </c>
+      <c r="B8" s="125" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
@@ -31816,283 +32341,4 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5038E81-DFEA-4A7B-94DE-1888A725E6E8}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="106.875" style="47" customWidth="1"/>
-    <col min="2" max="2" width="128.625" style="47" customWidth="1"/>
-    <col min="3" max="3" width="69" style="47" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="296" t="s">
-        <v>420</v>
-      </c>
-      <c r="B1" s="294"/>
-      <c r="C1" s="295"/>
-    </row>
-    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="300" t="s">
-        <v>422</v>
-      </c>
-      <c r="B2" s="301"/>
-      <c r="C2" s="309"/>
-    </row>
-    <row r="3" spans="1:3" ht="202.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="302" t="s">
-        <v>421</v>
-      </c>
-      <c r="B3" s="303" t="s">
-        <v>435</v>
-      </c>
-      <c r="C3" s="310" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="299" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="297"/>
-      <c r="C4" s="298"/>
-    </row>
-    <row r="5" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="478" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="304" t="s">
-        <v>426</v>
-      </c>
-      <c r="C5" s="309" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="479"/>
-      <c r="B6" s="305" t="s">
-        <v>441</v>
-      </c>
-      <c r="C6" s="311" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="480" t="s">
-        <v>423</v>
-      </c>
-      <c r="B7" s="306" t="s">
-        <v>434</v>
-      </c>
-      <c r="C7" s="314" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="288" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="480"/>
-      <c r="B8" s="305" t="s">
-        <v>424</v>
-      </c>
-      <c r="C8" s="311" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="480"/>
-      <c r="B9" s="305" t="s">
-        <v>425</v>
-      </c>
-      <c r="C9" s="312"/>
-    </row>
-    <row r="10" spans="1:3" ht="285" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="480" t="s">
-        <v>427</v>
-      </c>
-      <c r="B10" s="305" t="s">
-        <v>428</v>
-      </c>
-      <c r="C10" s="311" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="480"/>
-      <c r="B11" s="305" t="s">
-        <v>429</v>
-      </c>
-      <c r="C11" s="312" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="480"/>
-      <c r="B12" s="305" t="s">
-        <v>430</v>
-      </c>
-      <c r="C12" s="311" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="307" t="s">
-        <v>432</v>
-      </c>
-      <c r="B13" s="308"/>
-      <c r="C13" s="313" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" s="293"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03CDB98-0589-4698-B3D8-29BB64912381}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="73.625" style="177" customWidth="1"/>
-    <col min="2" max="2" width="182.625" style="177" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="177"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="281" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="B2" s="177" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="481" t="s">
-        <v>349</v>
-      </c>
-      <c r="B3" s="177" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="481"/>
-      <c r="B4" s="177" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="177" t="s">
-        <v>351</v>
-      </c>
-      <c r="B5" s="177" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="177" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="177" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="280"/>
-      <c r="B7" s="280"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="281" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="177" t="s">
-        <v>353</v>
-      </c>
-      <c r="B9" s="177" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="177" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="481" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" s="177" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="481"/>
-      <c r="B12" s="177" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="177" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13" s="177" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="177" t="s">
-        <v>355</v>
-      </c>
-      <c r="B14" s="177" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="177" t="s">
-        <v>356</v>
-      </c>
-      <c r="B15" s="177" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="282" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="283" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="283" t="s">
-        <v>404</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A11:A12"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>